--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_air_transport.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="brvm_abjc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,94 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.102</v>
+        <v>-0.0699</v>
+      </c>
+      <c r="E2">
+        <v>-0.0186</v>
       </c>
       <c r="G2">
-        <v>-0.1068376068376068</v>
+        <v>0.1472602739726027</v>
       </c>
       <c r="H2">
-        <v>-0.1068376068376068</v>
+        <v>0.1472602739726027</v>
       </c>
       <c r="I2">
-        <v>-0.05495726495726496</v>
+        <v>0.1075342465753425</v>
       </c>
       <c r="J2">
-        <v>-0.05495726495726496</v>
+        <v>0.1036982295922455</v>
       </c>
       <c r="K2">
-        <v>-0.618</v>
+        <v>1.65</v>
       </c>
       <c r="L2">
-        <v>-0.05282051282051282</v>
+        <v>0.113013698630137</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.2099</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.05260434782608696</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.7332727272727273</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.2099</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.05260434782608696</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.7332727272727273</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.2843478260869565</v>
+      </c>
+      <c r="W2">
+        <v>0.2904929577464789</v>
       </c>
       <c r="X2">
-        <v>0.08623946750561093</v>
+        <v>0.132158041690137</v>
+      </c>
+      <c r="Y2">
+        <v>0.1583349160563419</v>
+      </c>
+      <c r="Z2">
+        <v>17.56919374247893</v>
+      </c>
+      <c r="AA2">
+        <v>1.821894286458223</v>
       </c>
       <c r="AB2">
-        <v>0.08623946750561093</v>
+        <v>0.1319458268303122</v>
+      </c>
+      <c r="AC2">
+        <v>1.68994845962791</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>-6.451</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.003854649400147256</v>
+      </c>
+      <c r="AI2">
+        <v>0.01266182956323801</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>-0.3898120732370536</v>
+      </c>
+      <c r="AK2">
+        <v>-13.19222903885478</v>
       </c>
       <c r="AL2">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>-0.148</v>
+        <v>-0.144</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0.0413953488372093</v>
       </c>
       <c r="AO2">
-        <v>-214.3333333333333</v>
+        <v>1570</v>
       </c>
       <c r="AP2">
-        <v>-0</v>
+        <v>-3.00046511627907</v>
       </c>
       <c r="AQ2">
-        <v>4.344594594594595</v>
+        <v>-10.90277777777778</v>
       </c>
     </row>
     <row r="3">
@@ -695,94 +724,8833 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.102</v>
+        <v>-0.0699</v>
+      </c>
+      <c r="E3">
+        <v>-0.0186</v>
       </c>
       <c r="G3">
-        <v>-0.1068376068376068</v>
+        <v>0.1472602739726027</v>
       </c>
       <c r="H3">
-        <v>-0.1068376068376068</v>
+        <v>0.1472602739726027</v>
       </c>
       <c r="I3">
-        <v>-0.05495726495726496</v>
+        <v>0.1075342465753425</v>
       </c>
       <c r="J3">
-        <v>-0.05495726495726496</v>
+        <v>0.1036982295922455</v>
       </c>
       <c r="K3">
-        <v>-0.618</v>
+        <v>1.65</v>
       </c>
       <c r="L3">
-        <v>-0.05282051282051282</v>
+        <v>0.113013698630137</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.2099</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05260434782608696</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.7332727272727273</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.2099</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05260434782608696</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.7332727272727273</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2843478260869565</v>
+      </c>
+      <c r="W3">
+        <v>0.2904929577464789</v>
       </c>
       <c r="X3">
-        <v>0.08623946750561093</v>
+        <v>0.132158041690137</v>
+      </c>
+      <c r="Y3">
+        <v>0.1583349160563419</v>
+      </c>
+      <c r="Z3">
+        <v>17.56919374247893</v>
+      </c>
+      <c r="AA3">
+        <v>1.821894286458223</v>
       </c>
       <c r="AB3">
-        <v>0.08623946750561093</v>
+        <v>0.1319458268303122</v>
+      </c>
+      <c r="AC3">
+        <v>1.68994845962791</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-6.451</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.003854649400147256</v>
+      </c>
+      <c r="AI3">
+        <v>0.01266182956323801</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.3898120732370536</v>
+      </c>
+      <c r="AK3">
+        <v>-13.19222903885478</v>
       </c>
       <c r="AL3">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>-0.148</v>
+        <v>-0.144</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0.0413953488372093</v>
       </c>
       <c r="AO3">
-        <v>-214.3333333333333</v>
+        <v>1570</v>
       </c>
       <c r="AP3">
-        <v>-0</v>
+        <v>-3.00046511627907</v>
       </c>
       <c r="AQ3">
-        <v>4.344594594594595</v>
+        <v>-10.90277777777778</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Servair Abidjan S.A. (BRVM:ABJC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRVM:ABJC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.00385464940014726</v>
+      </c>
+      <c r="F2">
+        <v>0.27</v>
+      </c>
+      <c r="G2">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>17.787018458567</v>
+      </c>
+      <c r="I2">
+        <v>16.549</v>
+      </c>
+      <c r="J2">
+        <v>17.481048458567</v>
+      </c>
+      <c r="K2">
+        <v>0.089</v>
+      </c>
+      <c r="L2">
+        <v>6.23403</v>
+      </c>
+      <c r="M2">
+        <v>0.131945826830312</v>
+      </c>
+      <c r="N2">
+        <v>0.12626595225917</v>
+      </c>
+      <c r="O2">
+        <v>0.0771037844036697</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.132158041690137</v>
+      </c>
+      <c r="T2">
+        <v>0.157710208574206</v>
+      </c>
+      <c r="U2">
+        <v>0.770172823493083</v>
+      </c>
+      <c r="V2">
+        <v>0.980969709965786</v>
+      </c>
+      <c r="W2">
+        <v>4.581889462135467</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>23</v>
+      </c>
+      <c r="AB2">
+        <v>0.1212170033041622</v>
+      </c>
+      <c r="AC2">
+        <v>0.1028050458715596</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>2.15</v>
+      </c>
+      <c r="AH2">
+        <v>0.579</v>
+      </c>
+      <c r="AI2">
+        <v>0.03799999999999981</v>
+      </c>
+      <c r="AJ2">
+        <v>0.089</v>
+      </c>
+      <c r="AK2">
+        <v>0.089</v>
+      </c>
+      <c r="AL2">
+        <v>0.001</v>
+      </c>
+      <c r="AM2">
+        <v>0.089</v>
+      </c>
+      <c r="AN2">
+        <v>6.54</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1318878844602361</v>
+      </c>
+      <c r="C2">
+        <v>23.09800609584121</v>
+      </c>
+      <c r="D2">
+        <v>16.55800609584121</v>
+      </c>
+      <c r="E2">
+        <v>-0.089</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>6.54</v>
+      </c>
+      <c r="H2">
+        <v>23</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.15</v>
+      </c>
+      <c r="K2">
+        <v>0.579</v>
+      </c>
+      <c r="L2">
+        <v>1.571</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.571</v>
+      </c>
+      <c r="O2">
+        <v>0.39275</v>
+      </c>
+      <c r="P2">
+        <v>1.17825</v>
+      </c>
+      <c r="Q2">
+        <v>1.75725</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1318878844602361</v>
+      </c>
+      <c r="T2">
+        <v>0.7679441161126261</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1316099147490855</v>
+      </c>
+      <c r="C3">
+        <v>22.91045813953309</v>
+      </c>
+      <c r="D3">
+        <v>16.60134813953309</v>
+      </c>
+      <c r="E3">
+        <v>0.14189</v>
+      </c>
+      <c r="F3">
+        <v>0.23089</v>
+      </c>
+      <c r="G3">
+        <v>6.54</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.15</v>
+      </c>
+      <c r="K3">
+        <v>0.579</v>
+      </c>
+      <c r="L3">
+        <v>1.571</v>
+      </c>
+      <c r="M3">
+        <v>0.010551673</v>
+      </c>
+      <c r="N3">
+        <v>1.560448327</v>
+      </c>
+      <c r="O3">
+        <v>0.39011208175</v>
+      </c>
+      <c r="P3">
+        <v>1.17033624525</v>
+      </c>
+      <c r="Q3">
+        <v>1.74933624525</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.132593095706147</v>
+      </c>
+      <c r="T3">
+        <v>0.7737618745680248</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>148.8863424785814</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1313319450379349</v>
+      </c>
+      <c r="C4">
+        <v>22.72313768197947</v>
+      </c>
+      <c r="D4">
+        <v>16.64491768197947</v>
+      </c>
+      <c r="E4">
+        <v>0.37278</v>
+      </c>
+      <c r="F4">
+        <v>0.46178</v>
+      </c>
+      <c r="G4">
+        <v>6.54</v>
+      </c>
+      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.15</v>
+      </c>
+      <c r="K4">
+        <v>0.579</v>
+      </c>
+      <c r="L4">
+        <v>1.571</v>
+      </c>
+      <c r="M4">
+        <v>0.021103346</v>
+      </c>
+      <c r="N4">
+        <v>1.549896654</v>
+      </c>
+      <c r="O4">
+        <v>0.3874741635</v>
+      </c>
+      <c r="P4">
+        <v>1.1624224905</v>
+      </c>
+      <c r="Q4">
+        <v>1.7414224905</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.133312699018301</v>
+      </c>
+      <c r="T4">
+        <v>0.7796983627878195</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>74.44317123929066</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1310539753267843</v>
+      </c>
+      <c r="C5">
+        <v>22.53604651907644</v>
+      </c>
+      <c r="D5">
+        <v>16.68871651907644</v>
+      </c>
+      <c r="E5">
+        <v>0.6036699999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.6926699999999999</v>
+      </c>
+      <c r="G5">
+        <v>6.54</v>
+      </c>
+      <c r="H5">
+        <v>23</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.15</v>
+      </c>
+      <c r="K5">
+        <v>0.579</v>
+      </c>
+      <c r="L5">
+        <v>1.571</v>
+      </c>
+      <c r="M5">
+        <v>0.031655019</v>
+      </c>
+      <c r="N5">
+        <v>1.539344981</v>
+      </c>
+      <c r="O5">
+        <v>0.38483624525</v>
+      </c>
+      <c r="P5">
+        <v>1.15450873575</v>
+      </c>
+      <c r="Q5">
+        <v>1.73350873575</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1340471395121488</v>
+      </c>
+      <c r="T5">
+        <v>0.7857572528265787</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>49.62878082619378</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1307760056156338</v>
+      </c>
+      <c r="C6">
+        <v>22.34918646567258</v>
+      </c>
+      <c r="D6">
+        <v>16.73274646567258</v>
+      </c>
+      <c r="E6">
+        <v>0.83456</v>
+      </c>
+      <c r="F6">
+        <v>0.9235599999999999</v>
+      </c>
+      <c r="G6">
+        <v>6.54</v>
+      </c>
+      <c r="H6">
+        <v>23</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.15</v>
+      </c>
+      <c r="K6">
+        <v>0.579</v>
+      </c>
+      <c r="L6">
+        <v>1.571</v>
+      </c>
+      <c r="M6">
+        <v>0.042206692</v>
+      </c>
+      <c r="N6">
+        <v>1.528793308</v>
+      </c>
+      <c r="O6">
+        <v>0.382198327</v>
+      </c>
+      <c r="P6">
+        <v>1.146594981</v>
+      </c>
+      <c r="Q6">
+        <v>1.725594981</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1347968808496185</v>
+      </c>
+      <c r="T6">
+        <v>0.7919423697411457</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>37.22158561964534</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1304980359044832</v>
+      </c>
+      <c r="C7">
+        <v>22.16255935581968</v>
+      </c>
+      <c r="D7">
+        <v>16.77700935581968</v>
+      </c>
+      <c r="E7">
+        <v>1.06545</v>
+      </c>
+      <c r="F7">
+        <v>1.15445</v>
+      </c>
+      <c r="G7">
+        <v>6.54</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.15</v>
+      </c>
+      <c r="K7">
+        <v>0.579</v>
+      </c>
+      <c r="L7">
+        <v>1.571</v>
+      </c>
+      <c r="M7">
+        <v>0.052758365</v>
+      </c>
+      <c r="N7">
+        <v>1.518241635</v>
+      </c>
+      <c r="O7">
+        <v>0.37956040875</v>
+      </c>
+      <c r="P7">
+        <v>1.13868122625</v>
+      </c>
+      <c r="Q7">
+        <v>1.71768122625</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1355624062152454</v>
+      </c>
+      <c r="T7">
+        <v>0.7982576996433877</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.034275</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>29.77726849571627</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1302200661933325</v>
+      </c>
+      <c r="C8">
+        <v>21.97616704302731</v>
+      </c>
+      <c r="D8">
+        <v>16.82150704302731</v>
+      </c>
+      <c r="E8">
+        <v>1.29634</v>
+      </c>
+      <c r="F8">
+        <v>1.38534</v>
+      </c>
+      <c r="G8">
+        <v>6.54</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.15</v>
+      </c>
+      <c r="K8">
+        <v>0.579</v>
+      </c>
+      <c r="L8">
+        <v>1.571</v>
+      </c>
+      <c r="M8">
+        <v>0.063310038</v>
+      </c>
+      <c r="N8">
+        <v>1.507689962</v>
+      </c>
+      <c r="O8">
+        <v>0.3769224905</v>
+      </c>
+      <c r="P8">
+        <v>1.1307674715</v>
+      </c>
+      <c r="Q8">
+        <v>1.7097674715</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1363442193546091</v>
+      </c>
+      <c r="T8">
+        <v>0.8047073982669539</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.034275</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>24.81439041309689</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.129942096482182</v>
+      </c>
+      <c r="C9">
+        <v>21.79001140052163</v>
+      </c>
+      <c r="D9">
+        <v>16.86624140052163</v>
+      </c>
+      <c r="E9">
+        <v>1.52723</v>
+      </c>
+      <c r="F9">
+        <v>1.61623</v>
+      </c>
+      <c r="G9">
+        <v>6.54</v>
+      </c>
+      <c r="H9">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.15</v>
+      </c>
+      <c r="K9">
+        <v>0.579</v>
+      </c>
+      <c r="L9">
+        <v>1.571</v>
+      </c>
+      <c r="M9">
+        <v>0.07386171100000001</v>
+      </c>
+      <c r="N9">
+        <v>1.497138289</v>
+      </c>
+      <c r="O9">
+        <v>0.37428457225</v>
+      </c>
+      <c r="P9">
+        <v>1.12285371675</v>
+      </c>
+      <c r="Q9">
+        <v>1.70185371675</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1371428456797656</v>
+      </c>
+      <c r="T9">
+        <v>0.811295800086726</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.034275</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>21.26947749694019</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1296641267710314</v>
+      </c>
+      <c r="C10">
+        <v>21.60409432150821</v>
+      </c>
+      <c r="D10">
+        <v>16.91121432150821</v>
+      </c>
+      <c r="E10">
+        <v>1.75812</v>
+      </c>
+      <c r="F10">
+        <v>1.84712</v>
+      </c>
+      <c r="G10">
+        <v>6.54</v>
+      </c>
+      <c r="H10">
+        <v>23</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.15</v>
+      </c>
+      <c r="K10">
+        <v>0.579</v>
+      </c>
+      <c r="L10">
+        <v>1.571</v>
+      </c>
+      <c r="M10">
+        <v>0.08441338400000001</v>
+      </c>
+      <c r="N10">
+        <v>1.486586616</v>
+      </c>
+      <c r="O10">
+        <v>0.371646654</v>
+      </c>
+      <c r="P10">
+        <v>1.114939962</v>
+      </c>
+      <c r="Q10">
+        <v>1.693939962</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1379588334467733</v>
+      </c>
+      <c r="T10">
+        <v>0.8180274280330149</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.034275</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>18.61079280982267</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1293861570598808</v>
+      </c>
+      <c r="C11">
+        <v>21.41841771943916</v>
+      </c>
+      <c r="D11">
+        <v>16.95642771943916</v>
+      </c>
+      <c r="E11">
+        <v>1.98901</v>
+      </c>
+      <c r="F11">
+        <v>2.07801</v>
+      </c>
+      <c r="G11">
+        <v>6.54</v>
+      </c>
+      <c r="H11">
+        <v>23</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.15</v>
+      </c>
+      <c r="K11">
+        <v>0.579</v>
+      </c>
+      <c r="L11">
+        <v>1.571</v>
+      </c>
+      <c r="M11">
+        <v>0.09496505700000001</v>
+      </c>
+      <c r="N11">
+        <v>1.476034943</v>
+      </c>
+      <c r="O11">
+        <v>0.36900873575</v>
+      </c>
+      <c r="P11">
+        <v>1.10702620725</v>
+      </c>
+      <c r="Q11">
+        <v>1.68602620725</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.138792755010858</v>
+      </c>
+      <c r="T11">
+        <v>0.8249070038462549</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.034275</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>16.54292694206459</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1291081873487302</v>
+      </c>
+      <c r="C12">
+        <v>21.23298352828443</v>
+      </c>
+      <c r="D12">
+        <v>17.00188352828443</v>
+      </c>
+      <c r="E12">
+        <v>2.2199</v>
+      </c>
+      <c r="F12">
+        <v>2.3089</v>
+      </c>
+      <c r="G12">
+        <v>6.54</v>
+      </c>
+      <c r="H12">
+        <v>23</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.15</v>
+      </c>
+      <c r="K12">
+        <v>0.579</v>
+      </c>
+      <c r="L12">
+        <v>1.571</v>
+      </c>
+      <c r="M12">
+        <v>0.10551673</v>
+      </c>
+      <c r="N12">
+        <v>1.46548327</v>
+      </c>
+      <c r="O12">
+        <v>0.3663708175</v>
+      </c>
+      <c r="P12">
+        <v>1.0991124525</v>
+      </c>
+      <c r="Q12">
+        <v>1.6781124525</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1396452081652558</v>
+      </c>
+      <c r="T12">
+        <v>0.8319394591220116</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.034275</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.88863424785814</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1288302176375796</v>
+      </c>
+      <c r="C13">
+        <v>21.04779370280763</v>
+      </c>
+      <c r="D13">
+        <v>17.04758370280764</v>
+      </c>
+      <c r="E13">
+        <v>2.45079</v>
+      </c>
+      <c r="F13">
+        <v>2.53979</v>
+      </c>
+      <c r="G13">
+        <v>6.54</v>
+      </c>
+      <c r="H13">
+        <v>23</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.15</v>
+      </c>
+      <c r="K13">
+        <v>0.579</v>
+      </c>
+      <c r="L13">
+        <v>1.571</v>
+      </c>
+      <c r="M13">
+        <v>0.116068403</v>
+      </c>
+      <c r="N13">
+        <v>1.454931597</v>
+      </c>
+      <c r="O13">
+        <v>0.36373289925</v>
+      </c>
+      <c r="P13">
+        <v>1.09119869775</v>
+      </c>
+      <c r="Q13">
+        <v>1.67019869775</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1405168175703142</v>
+      </c>
+      <c r="T13">
+        <v>0.8391299471005943</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.034275</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>13.53512204350739</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.128696247926429</v>
+      </c>
+      <c r="C14">
+        <v>20.83901711606736</v>
+      </c>
+      <c r="D14">
+        <v>17.06969711606736</v>
+      </c>
+      <c r="E14">
+        <v>2.68168</v>
+      </c>
+      <c r="F14">
+        <v>2.77068</v>
+      </c>
+      <c r="G14">
+        <v>6.54</v>
+      </c>
+      <c r="H14">
+        <v>23</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.15</v>
+      </c>
+      <c r="K14">
+        <v>0.579</v>
+      </c>
+      <c r="L14">
+        <v>1.571</v>
+      </c>
+      <c r="M14">
+        <v>0.131053164</v>
+      </c>
+      <c r="N14">
+        <v>1.439946836</v>
+      </c>
+      <c r="O14">
+        <v>0.359986709</v>
+      </c>
+      <c r="P14">
+        <v>1.079960127</v>
+      </c>
+      <c r="Q14">
+        <v>1.658960127</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.141408236280033</v>
+      </c>
+      <c r="T14">
+        <v>0.8464838552605084</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.035475</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.98750149977303</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1284302782152784</v>
+      </c>
+      <c r="C15">
+        <v>20.65219926059461</v>
+      </c>
+      <c r="D15">
+        <v>17.11376926059462</v>
+      </c>
+      <c r="E15">
+        <v>2.91257</v>
+      </c>
+      <c r="F15">
+        <v>3.00157</v>
+      </c>
+      <c r="G15">
+        <v>6.54</v>
+      </c>
+      <c r="H15">
+        <v>23</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.15</v>
+      </c>
+      <c r="K15">
+        <v>0.579</v>
+      </c>
+      <c r="L15">
+        <v>1.571</v>
+      </c>
+      <c r="M15">
+        <v>0.141974261</v>
+      </c>
+      <c r="N15">
+        <v>1.429025739</v>
+      </c>
+      <c r="O15">
+        <v>0.35725643475</v>
+      </c>
+      <c r="P15">
+        <v>1.07176930425</v>
+      </c>
+      <c r="Q15">
+        <v>1.65076930425</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1423201473738833</v>
+      </c>
+      <c r="T15">
+        <v>0.8540068187804204</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.035475</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>11.06538599979048</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1281643085041279</v>
+      </c>
+      <c r="C16">
+        <v>20.46560957341836</v>
+      </c>
+      <c r="D16">
+        <v>17.15806957341836</v>
+      </c>
+      <c r="E16">
+        <v>3.14346</v>
+      </c>
+      <c r="F16">
+        <v>3.23246</v>
+      </c>
+      <c r="G16">
+        <v>6.54</v>
+      </c>
+      <c r="H16">
+        <v>23</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.15</v>
+      </c>
+      <c r="K16">
+        <v>0.579</v>
+      </c>
+      <c r="L16">
+        <v>1.571</v>
+      </c>
+      <c r="M16">
+        <v>0.152895358</v>
+      </c>
+      <c r="N16">
+        <v>1.418104642</v>
+      </c>
+      <c r="O16">
+        <v>0.3545261605</v>
+      </c>
+      <c r="P16">
+        <v>1.0635784815</v>
+      </c>
+      <c r="Q16">
+        <v>1.6425784815</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1432532657024743</v>
+      </c>
+      <c r="T16">
+        <v>0.8617047349403305</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.035475</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>10.27500128551973</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1283258387929772</v>
+      </c>
+      <c r="C17">
+        <v>20.20778754210545</v>
+      </c>
+      <c r="D17">
+        <v>17.13113754210545</v>
+      </c>
+      <c r="E17">
+        <v>3.37435</v>
+      </c>
+      <c r="F17">
+        <v>3.46335</v>
+      </c>
+      <c r="G17">
+        <v>6.54</v>
+      </c>
+      <c r="H17">
+        <v>23</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.15</v>
+      </c>
+      <c r="K17">
+        <v>0.579</v>
+      </c>
+      <c r="L17">
+        <v>1.571</v>
+      </c>
+      <c r="M17">
+        <v>0.176977185</v>
+      </c>
+      <c r="N17">
+        <v>1.394022815</v>
+      </c>
+      <c r="O17">
+        <v>0.34850570375</v>
+      </c>
+      <c r="P17">
+        <v>1.04551711125</v>
+      </c>
+      <c r="Q17">
+        <v>1.62451711125</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1442083397564438</v>
+      </c>
+      <c r="T17">
+        <v>0.8695837785392972</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.038325</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.876850425663626</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1280883690818266</v>
+      </c>
+      <c r="C18">
+        <v>20.01652027854258</v>
+      </c>
+      <c r="D18">
+        <v>17.17076027854258</v>
+      </c>
+      <c r="E18">
+        <v>3.60524</v>
+      </c>
+      <c r="F18">
+        <v>3.69424</v>
+      </c>
+      <c r="G18">
+        <v>6.54</v>
+      </c>
+      <c r="H18">
+        <v>23</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.15</v>
+      </c>
+      <c r="K18">
+        <v>0.579</v>
+      </c>
+      <c r="L18">
+        <v>1.571</v>
+      </c>
+      <c r="M18">
+        <v>0.188775664</v>
+      </c>
+      <c r="N18">
+        <v>1.382224336</v>
+      </c>
+      <c r="O18">
+        <v>0.345556084</v>
+      </c>
+      <c r="P18">
+        <v>1.036668252</v>
+      </c>
+      <c r="Q18">
+        <v>1.615668252</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1451861536688412</v>
+      </c>
+      <c r="T18">
+        <v>0.8776504184144298</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.038325</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.322047274059649</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1278508993706761</v>
+      </c>
+      <c r="C19">
+        <v>19.82543672733763</v>
+      </c>
+      <c r="D19">
+        <v>17.21056672733763</v>
+      </c>
+      <c r="E19">
+        <v>3.83613</v>
+      </c>
+      <c r="F19">
+        <v>3.92513</v>
+      </c>
+      <c r="G19">
+        <v>6.54</v>
+      </c>
+      <c r="H19">
+        <v>23</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.15</v>
+      </c>
+      <c r="K19">
+        <v>0.579</v>
+      </c>
+      <c r="L19">
+        <v>1.571</v>
+      </c>
+      <c r="M19">
+        <v>0.200574143</v>
+      </c>
+      <c r="N19">
+        <v>1.370425857</v>
+      </c>
+      <c r="O19">
+        <v>0.34260646425</v>
+      </c>
+      <c r="P19">
+        <v>1.02781939275</v>
+      </c>
+      <c r="Q19">
+        <v>1.60681939275</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1461875293622603</v>
+      </c>
+      <c r="T19">
+        <v>0.8859114351540236</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.038325</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.832515081467903</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1278699296595255</v>
+      </c>
+      <c r="C20">
+        <v>19.59134992663768</v>
+      </c>
+      <c r="D20">
+        <v>17.20736992663768</v>
+      </c>
+      <c r="E20">
+        <v>4.067019999999999</v>
+      </c>
+      <c r="F20">
+        <v>4.15602</v>
+      </c>
+      <c r="G20">
+        <v>6.54</v>
+      </c>
+      <c r="H20">
+        <v>23</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.15</v>
+      </c>
+      <c r="K20">
+        <v>0.579</v>
+      </c>
+      <c r="L20">
+        <v>1.571</v>
+      </c>
+      <c r="M20">
+        <v>0.22026906</v>
+      </c>
+      <c r="N20">
+        <v>1.35073094</v>
+      </c>
+      <c r="O20">
+        <v>0.337682735</v>
+      </c>
+      <c r="P20">
+        <v>1.013048205</v>
+      </c>
+      <c r="Q20">
+        <v>1.592048205</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1472133288530799</v>
+      </c>
+      <c r="T20">
+        <v>0.894373940106778</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>7.132186426908981</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1276467099483749</v>
+      </c>
+      <c r="C21">
+        <v>19.39803235791883</v>
+      </c>
+      <c r="D21">
+        <v>17.24494235791883</v>
+      </c>
+      <c r="E21">
+        <v>4.297909999999999</v>
+      </c>
+      <c r="F21">
+        <v>4.386909999999999</v>
+      </c>
+      <c r="G21">
+        <v>6.54</v>
+      </c>
+      <c r="H21">
+        <v>23</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.15</v>
+      </c>
+      <c r="K21">
+        <v>0.579</v>
+      </c>
+      <c r="L21">
+        <v>1.571</v>
+      </c>
+      <c r="M21">
+        <v>0.23250623</v>
+      </c>
+      <c r="N21">
+        <v>1.33849377</v>
+      </c>
+      <c r="O21">
+        <v>0.3346234425</v>
+      </c>
+      <c r="P21">
+        <v>1.0038703275</v>
+      </c>
+      <c r="Q21">
+        <v>1.5828703275</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1482644567263888</v>
+      </c>
+      <c r="T21">
+        <v>0.9030453957991068</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.756808193913772</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1274234902372243</v>
+      </c>
+      <c r="C22">
+        <v>19.20487922766734</v>
+      </c>
+      <c r="D22">
+        <v>17.28267922766734</v>
+      </c>
+      <c r="E22">
+        <v>4.528799999999999</v>
+      </c>
+      <c r="F22">
+        <v>4.6178</v>
+      </c>
+      <c r="G22">
+        <v>6.54</v>
+      </c>
+      <c r="H22">
+        <v>23</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.15</v>
+      </c>
+      <c r="K22">
+        <v>0.579</v>
+      </c>
+      <c r="L22">
+        <v>1.571</v>
+      </c>
+      <c r="M22">
+        <v>0.2447434</v>
+      </c>
+      <c r="N22">
+        <v>1.3262566</v>
+      </c>
+      <c r="O22">
+        <v>0.33156415</v>
+      </c>
+      <c r="P22">
+        <v>0.9946924500000001</v>
+      </c>
+      <c r="Q22">
+        <v>1.57369245</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1493418627965304</v>
+      </c>
+      <c r="T22">
+        <v>0.9119336378837435</v>
+      </c>
+      <c r="U22">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.418967784218083</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1275152705260737</v>
+      </c>
+      <c r="C23">
+        <v>18.95845314607119</v>
+      </c>
+      <c r="D23">
+        <v>17.26714314607119</v>
+      </c>
+      <c r="E23">
+        <v>4.759689999999999</v>
+      </c>
+      <c r="F23">
+        <v>4.84869</v>
+      </c>
+      <c r="G23">
+        <v>6.54</v>
+      </c>
+      <c r="H23">
+        <v>23</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.15</v>
+      </c>
+      <c r="K23">
+        <v>0.579</v>
+      </c>
+      <c r="L23">
+        <v>1.571</v>
+      </c>
+      <c r="M23">
+        <v>0.26667795</v>
+      </c>
+      <c r="N23">
+        <v>1.30432205</v>
+      </c>
+      <c r="O23">
+        <v>0.3260805125</v>
+      </c>
+      <c r="P23">
+        <v>0.9782415375</v>
+      </c>
+      <c r="Q23">
+        <v>1.5572415375</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1504465449697135</v>
+      </c>
+      <c r="T23">
+        <v>0.9210468987553332</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.04125</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.891000737031314</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1273070508149231</v>
+      </c>
+      <c r="C24">
+        <v>18.76284975614588</v>
+      </c>
+      <c r="D24">
+        <v>17.30242975614588</v>
+      </c>
+      <c r="E24">
+        <v>4.99058</v>
+      </c>
+      <c r="F24">
+        <v>5.07958</v>
+      </c>
+      <c r="G24">
+        <v>6.54</v>
+      </c>
+      <c r="H24">
+        <v>23</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.15</v>
+      </c>
+      <c r="K24">
+        <v>0.579</v>
+      </c>
+      <c r="L24">
+        <v>1.571</v>
+      </c>
+      <c r="M24">
+        <v>0.2793769</v>
+      </c>
+      <c r="N24">
+        <v>1.2916231</v>
+      </c>
+      <c r="O24">
+        <v>0.322905775</v>
+      </c>
+      <c r="P24">
+        <v>0.9687173250000001</v>
+      </c>
+      <c r="Q24">
+        <v>1.547717325</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1515795523268245</v>
+      </c>
+      <c r="T24">
+        <v>0.9303938329826047</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.04125</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.623227976257164</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1270988311037725</v>
+      </c>
+      <c r="C25">
+        <v>18.56739088284279</v>
+      </c>
+      <c r="D25">
+        <v>17.33786088284279</v>
+      </c>
+      <c r="E25">
+        <v>5.221469999999999</v>
+      </c>
+      <c r="F25">
+        <v>5.31047</v>
+      </c>
+      <c r="G25">
+        <v>6.54</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.15</v>
+      </c>
+      <c r="K25">
+        <v>0.579</v>
+      </c>
+      <c r="L25">
+        <v>1.571</v>
+      </c>
+      <c r="M25">
+        <v>0.29207585</v>
+      </c>
+      <c r="N25">
+        <v>1.27892415</v>
+      </c>
+      <c r="O25">
+        <v>0.3197310375</v>
+      </c>
+      <c r="P25">
+        <v>0.9591931124999999</v>
+      </c>
+      <c r="Q25">
+        <v>1.5381931125</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1527419884464578</v>
+      </c>
+      <c r="T25">
+        <v>0.9399835447222729</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.04125</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.378739803376417</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1268906113926219</v>
+      </c>
+      <c r="C26">
+        <v>18.3720774157873</v>
+      </c>
+      <c r="D26">
+        <v>17.3734374157873</v>
+      </c>
+      <c r="E26">
+        <v>5.452359999999999</v>
+      </c>
+      <c r="F26">
+        <v>5.541359999999999</v>
+      </c>
+      <c r="G26">
+        <v>6.54</v>
+      </c>
+      <c r="H26">
+        <v>23</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.15</v>
+      </c>
+      <c r="K26">
+        <v>0.579</v>
+      </c>
+      <c r="L26">
+        <v>1.571</v>
+      </c>
+      <c r="M26">
+        <v>0.3047748</v>
+      </c>
+      <c r="N26">
+        <v>1.2662252</v>
+      </c>
+      <c r="O26">
+        <v>0.3165563</v>
+      </c>
+      <c r="P26">
+        <v>0.9496689</v>
+      </c>
+      <c r="Q26">
+        <v>1.5286689</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1539350149902921</v>
+      </c>
+      <c r="T26">
+        <v>0.9498256172971955</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.04125</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.154625644902401</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1266823916814714</v>
+      </c>
+      <c r="C27">
+        <v>18.1769102519217</v>
+      </c>
+      <c r="D27">
+        <v>17.4091602519217</v>
+      </c>
+      <c r="E27">
+        <v>5.683249999999999</v>
+      </c>
+      <c r="F27">
+        <v>5.77225</v>
+      </c>
+      <c r="G27">
+        <v>6.54</v>
+      </c>
+      <c r="H27">
+        <v>23</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.15</v>
+      </c>
+      <c r="K27">
+        <v>0.579</v>
+      </c>
+      <c r="L27">
+        <v>1.571</v>
+      </c>
+      <c r="M27">
+        <v>0.31747375</v>
+      </c>
+      <c r="N27">
+        <v>1.25352625</v>
+      </c>
+      <c r="O27">
+        <v>0.3133815625</v>
+      </c>
+      <c r="P27">
+        <v>0.9401446874999999</v>
+      </c>
+      <c r="Q27">
+        <v>1.5191446875</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1551598555752952</v>
+      </c>
+      <c r="T27">
+        <v>0.9599301451407827</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.04125</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.948440619106304</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1264741719703208</v>
+      </c>
+      <c r="C28">
+        <v>17.98189029558054</v>
+      </c>
+      <c r="D28">
+        <v>17.44503029558054</v>
+      </c>
+      <c r="E28">
+        <v>5.91414</v>
+      </c>
+      <c r="F28">
+        <v>6.00314</v>
+      </c>
+      <c r="G28">
+        <v>6.54</v>
+      </c>
+      <c r="H28">
+        <v>23</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.15</v>
+      </c>
+      <c r="K28">
+        <v>0.579</v>
+      </c>
+      <c r="L28">
+        <v>1.571</v>
+      </c>
+      <c r="M28">
+        <v>0.3301727</v>
+      </c>
+      <c r="N28">
+        <v>1.2408273</v>
+      </c>
+      <c r="O28">
+        <v>0.310206825</v>
+      </c>
+      <c r="P28">
+        <v>0.9306204749999999</v>
+      </c>
+      <c r="Q28">
+        <v>1.509620475</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1564177999598929</v>
+      </c>
+      <c r="T28">
+        <v>0.9703077683314939</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.04125</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.758115979909908</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1262659522591702</v>
+      </c>
+      <c r="C29">
+        <v>17.78701845856702</v>
+      </c>
+      <c r="D29">
+        <v>17.48104845856702</v>
+      </c>
+      <c r="E29">
+        <v>6.145029999999999</v>
+      </c>
+      <c r="F29">
+        <v>6.23403</v>
+      </c>
+      <c r="G29">
+        <v>6.54</v>
+      </c>
+      <c r="H29">
+        <v>23</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.15</v>
+      </c>
+      <c r="K29">
+        <v>0.579</v>
+      </c>
+      <c r="L29">
+        <v>1.571</v>
+      </c>
+      <c r="M29">
+        <v>0.34287165</v>
+      </c>
+      <c r="N29">
+        <v>1.22812835</v>
+      </c>
+      <c r="O29">
+        <v>0.3070320875</v>
+      </c>
+      <c r="P29">
+        <v>0.9210962625</v>
+      </c>
+      <c r="Q29">
+        <v>1.5000962625</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1577102085742057</v>
+      </c>
+      <c r="T29">
+        <v>0.9809697099657863</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.04125</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.581889462135467</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1268557325480196</v>
+      </c>
+      <c r="C30">
+        <v>17.454491115884</v>
+      </c>
+      <c r="D30">
+        <v>17.379411115884</v>
+      </c>
+      <c r="E30">
+        <v>6.37592</v>
+      </c>
+      <c r="F30">
+        <v>6.46492</v>
+      </c>
+      <c r="G30">
+        <v>6.54</v>
+      </c>
+      <c r="H30">
+        <v>23</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.15</v>
+      </c>
+      <c r="K30">
+        <v>0.579</v>
+      </c>
+      <c r="L30">
+        <v>1.571</v>
+      </c>
+      <c r="M30">
+        <v>0.3801372960000001</v>
+      </c>
+      <c r="N30">
+        <v>1.190862704</v>
+      </c>
+      <c r="O30">
+        <v>0.297715676</v>
+      </c>
+      <c r="P30">
+        <v>0.893147028</v>
+      </c>
+      <c r="Q30">
+        <v>1.472147028</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.159038517427805</v>
+      </c>
+      <c r="T30">
+        <v>0.9919278166454755</v>
+      </c>
+      <c r="U30">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.0441</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.132717353784722</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.127589512836869</v>
+      </c>
+      <c r="C31">
+        <v>17.09878622154572</v>
+      </c>
+      <c r="D31">
+        <v>17.25459622154572</v>
+      </c>
+      <c r="E31">
+        <v>6.606809999999999</v>
+      </c>
+      <c r="F31">
+        <v>6.695809999999999</v>
+      </c>
+      <c r="G31">
+        <v>6.54</v>
+      </c>
+      <c r="H31">
+        <v>23</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.15</v>
+      </c>
+      <c r="K31">
+        <v>0.579</v>
+      </c>
+      <c r="L31">
+        <v>1.571</v>
+      </c>
+      <c r="M31">
+        <v>0.4218360299999999</v>
+      </c>
+      <c r="N31">
+        <v>1.14916397</v>
+      </c>
+      <c r="O31">
+        <v>0.2872909925</v>
+      </c>
+      <c r="P31">
+        <v>0.8618729775</v>
+      </c>
+      <c r="Q31">
+        <v>1.4408729775</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1604042434322098</v>
+      </c>
+      <c r="T31">
+        <v>1.003194602386564</v>
+      </c>
+      <c r="U31">
+        <v>0.063</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.04725</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.724195868238188</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1274412931257184</v>
+      </c>
+      <c r="C32">
+        <v>16.89296346378512</v>
+      </c>
+      <c r="D32">
+        <v>17.27966346378512</v>
+      </c>
+      <c r="E32">
+        <v>6.837699999999999</v>
+      </c>
+      <c r="F32">
+        <v>6.926699999999999</v>
+      </c>
+      <c r="G32">
+        <v>6.54</v>
+      </c>
+      <c r="H32">
+        <v>23</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.15</v>
+      </c>
+      <c r="K32">
+        <v>0.579</v>
+      </c>
+      <c r="L32">
+        <v>1.571</v>
+      </c>
+      <c r="M32">
+        <v>0.4363820999999999</v>
+      </c>
+      <c r="N32">
+        <v>1.1346179</v>
+      </c>
+      <c r="O32">
+        <v>0.283654475</v>
+      </c>
+      <c r="P32">
+        <v>0.850963425</v>
+      </c>
+      <c r="Q32">
+        <v>1.429963425</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1618089901795977</v>
+      </c>
+      <c r="T32">
+        <v>1.014783296291685</v>
+      </c>
+      <c r="U32">
+        <v>0.063</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.04725</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.600056005963582</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1289438234145678</v>
+      </c>
+      <c r="C33">
+        <v>16.41128646111502</v>
+      </c>
+      <c r="D33">
+        <v>17.02887646111502</v>
+      </c>
+      <c r="E33">
+        <v>7.068589999999999</v>
+      </c>
+      <c r="F33">
+        <v>7.15759</v>
+      </c>
+      <c r="G33">
+        <v>6.54</v>
+      </c>
+      <c r="H33">
+        <v>23</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.15</v>
+      </c>
+      <c r="K33">
+        <v>0.579</v>
+      </c>
+      <c r="L33">
+        <v>1.571</v>
+      </c>
+      <c r="M33">
+        <v>0.5017470589999999</v>
+      </c>
+      <c r="N33">
+        <v>1.069252941</v>
+      </c>
+      <c r="O33">
+        <v>0.26731323525</v>
+      </c>
+      <c r="P33">
+        <v>0.80193970575</v>
+      </c>
+      <c r="Q33">
+        <v>1.38093970575</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1632544542240113</v>
+      </c>
+      <c r="T33">
+        <v>1.026707894367967</v>
+      </c>
+      <c r="U33">
+        <v>0.0701</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.052575</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.131059707915498</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1288488537034172</v>
+      </c>
+      <c r="C34">
+        <v>16.19603212050471</v>
+      </c>
+      <c r="D34">
+        <v>17.04451212050471</v>
+      </c>
+      <c r="E34">
+        <v>7.299479999999999</v>
+      </c>
+      <c r="F34">
+        <v>7.388479999999999</v>
+      </c>
+      <c r="G34">
+        <v>6.54</v>
+      </c>
+      <c r="H34">
+        <v>23</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.15</v>
+      </c>
+      <c r="K34">
+        <v>0.579</v>
+      </c>
+      <c r="L34">
+        <v>1.571</v>
+      </c>
+      <c r="M34">
+        <v>0.5179324479999999</v>
+      </c>
+      <c r="N34">
+        <v>1.053067552</v>
+      </c>
+      <c r="O34">
+        <v>0.263266888</v>
+      </c>
+      <c r="P34">
+        <v>0.7898006639999999</v>
+      </c>
+      <c r="Q34">
+        <v>1.368800664</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.16474243191679</v>
+      </c>
+      <c r="T34">
+        <v>1.038983215917082</v>
+      </c>
+      <c r="U34">
+        <v>0.0701</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.052575</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.033214092043139</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1340256339922666</v>
+      </c>
+      <c r="C35">
+        <v>15.15272440996843</v>
+      </c>
+      <c r="D35">
+        <v>16.23209440996843</v>
+      </c>
+      <c r="E35">
+        <v>7.53037</v>
+      </c>
+      <c r="F35">
+        <v>7.61937</v>
+      </c>
+      <c r="G35">
+        <v>6.54</v>
+      </c>
+      <c r="H35">
+        <v>23</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.15</v>
+      </c>
+      <c r="K35">
+        <v>0.579</v>
+      </c>
+      <c r="L35">
+        <v>1.571</v>
+      </c>
+      <c r="M35">
+        <v>0.696410418</v>
+      </c>
+      <c r="N35">
+        <v>0.8745895819999999</v>
+      </c>
+      <c r="O35">
+        <v>0.2186473955</v>
+      </c>
+      <c r="P35">
+        <v>0.6559421864999999</v>
+      </c>
+      <c r="Q35">
+        <v>1.2349421865</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1662748268541293</v>
+      </c>
+      <c r="T35">
+        <v>1.051624964975126</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.06855</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.255853673917899</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.134090414281116</v>
+      </c>
+      <c r="C36">
+        <v>14.91215846132285</v>
+      </c>
+      <c r="D36">
+        <v>16.22241846132285</v>
+      </c>
+      <c r="E36">
+        <v>7.76126</v>
+      </c>
+      <c r="F36">
+        <v>7.85026</v>
+      </c>
+      <c r="G36">
+        <v>6.54</v>
+      </c>
+      <c r="H36">
+        <v>23</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.15</v>
+      </c>
+      <c r="K36">
+        <v>0.579</v>
+      </c>
+      <c r="L36">
+        <v>1.571</v>
+      </c>
+      <c r="M36">
+        <v>0.7175137640000001</v>
+      </c>
+      <c r="N36">
+        <v>0.8534862359999998</v>
+      </c>
+      <c r="O36">
+        <v>0.213371559</v>
+      </c>
+      <c r="P36">
+        <v>0.6401146769999999</v>
+      </c>
+      <c r="Q36">
+        <v>1.219114677</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.167853658001691</v>
+      </c>
+      <c r="T36">
+        <v>1.064649797337959</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.06855</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.189505036449725</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1341551945699654</v>
+      </c>
+      <c r="C37">
+        <v>14.67160404146757</v>
+      </c>
+      <c r="D37">
+        <v>16.21275404146757</v>
+      </c>
+      <c r="E37">
+        <v>7.992150000000001</v>
+      </c>
+      <c r="F37">
+        <v>8.081150000000001</v>
+      </c>
+      <c r="G37">
+        <v>6.54</v>
+      </c>
+      <c r="H37">
+        <v>23</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.15</v>
+      </c>
+      <c r="K37">
+        <v>0.579</v>
+      </c>
+      <c r="L37">
+        <v>1.571</v>
+      </c>
+      <c r="M37">
+        <v>0.7386171100000002</v>
+      </c>
+      <c r="N37">
+        <v>0.8323828899999998</v>
+      </c>
+      <c r="O37">
+        <v>0.2080957224999999</v>
+      </c>
+      <c r="P37">
+        <v>0.6242871674999998</v>
+      </c>
+      <c r="Q37">
+        <v>1.2032871675</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1694810685691776</v>
+      </c>
+      <c r="T37">
+        <v>1.078075393773494</v>
+      </c>
+      <c r="U37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.06855</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.126947749694019</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1342199748588149</v>
+      </c>
+      <c r="C38">
+        <v>14.43106112981019</v>
+      </c>
+      <c r="D38">
+        <v>16.20310112981019</v>
+      </c>
+      <c r="E38">
+        <v>8.223039999999999</v>
+      </c>
+      <c r="F38">
+        <v>8.31204</v>
+      </c>
+      <c r="G38">
+        <v>6.54</v>
+      </c>
+      <c r="H38">
+        <v>23</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.15</v>
+      </c>
+      <c r="K38">
+        <v>0.579</v>
+      </c>
+      <c r="L38">
+        <v>1.571</v>
+      </c>
+      <c r="M38">
+        <v>0.759720456</v>
+      </c>
+      <c r="N38">
+        <v>0.8112795439999999</v>
+      </c>
+      <c r="O38">
+        <v>0.202819886</v>
+      </c>
+      <c r="P38">
+        <v>0.6084596579999999</v>
+      </c>
+      <c r="Q38">
+        <v>1.187459658</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1711593357168982</v>
+      </c>
+      <c r="T38">
+        <v>1.09192054009764</v>
+      </c>
+      <c r="U38">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.06855</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.067865867758075</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1342847551476643</v>
+      </c>
+      <c r="C39">
+        <v>14.19052970580736</v>
+      </c>
+      <c r="D39">
+        <v>16.19345970580736</v>
+      </c>
+      <c r="E39">
+        <v>8.45393</v>
+      </c>
+      <c r="F39">
+        <v>8.54293</v>
+      </c>
+      <c r="G39">
+        <v>6.54</v>
+      </c>
+      <c r="H39">
+        <v>23</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.15</v>
+      </c>
+      <c r="K39">
+        <v>0.579</v>
+      </c>
+      <c r="L39">
+        <v>1.571</v>
+      </c>
+      <c r="M39">
+        <v>0.7808238020000001</v>
+      </c>
+      <c r="N39">
+        <v>0.7901761979999998</v>
+      </c>
+      <c r="O39">
+        <v>0.1975440495</v>
+      </c>
+      <c r="P39">
+        <v>0.5926321484999999</v>
+      </c>
+      <c r="Q39">
+        <v>1.1716321485</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1728908811867687</v>
+      </c>
+      <c r="T39">
+        <v>1.106205214876521</v>
+      </c>
+      <c r="U39">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.06855</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.01197760106191</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1403630354365137</v>
+      </c>
+      <c r="C40">
+        <v>13.10333993296256</v>
+      </c>
+      <c r="D40">
+        <v>15.33715993296256</v>
+      </c>
+      <c r="E40">
+        <v>8.684819999999998</v>
+      </c>
+      <c r="F40">
+        <v>8.773819999999999</v>
+      </c>
+      <c r="G40">
+        <v>6.54</v>
+      </c>
+      <c r="H40">
+        <v>23</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.15</v>
+      </c>
+      <c r="K40">
+        <v>0.579</v>
+      </c>
+      <c r="L40">
+        <v>1.571</v>
+      </c>
+      <c r="M40">
+        <v>0.9870547499999999</v>
+      </c>
+      <c r="N40">
+        <v>0.5839452500000001</v>
+      </c>
+      <c r="O40">
+        <v>0.1459863125</v>
+      </c>
+      <c r="P40">
+        <v>0.4379589375</v>
+      </c>
+      <c r="Q40">
+        <v>1.0169589375</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1746782829621188</v>
+      </c>
+      <c r="T40">
+        <v>1.120950685616011</v>
+      </c>
+      <c r="U40">
+        <v>0.1125</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.591603707899689</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1405860657253631</v>
+      </c>
+      <c r="C41">
+        <v>12.84274884156751</v>
+      </c>
+      <c r="D41">
+        <v>15.30745884156751</v>
+      </c>
+      <c r="E41">
+        <v>8.915709999999999</v>
+      </c>
+      <c r="F41">
+        <v>9.004709999999999</v>
+      </c>
+      <c r="G41">
+        <v>6.54</v>
+      </c>
+      <c r="H41">
+        <v>23</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.15</v>
+      </c>
+      <c r="K41">
+        <v>0.579</v>
+      </c>
+      <c r="L41">
+        <v>1.571</v>
+      </c>
+      <c r="M41">
+        <v>1.013029875</v>
+      </c>
+      <c r="N41">
+        <v>0.557970125</v>
+      </c>
+      <c r="O41">
+        <v>0.13949253125</v>
+      </c>
+      <c r="P41">
+        <v>0.41847759375</v>
+      </c>
+      <c r="Q41">
+        <v>0.99747759375</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1765242880743657</v>
+      </c>
+      <c r="T41">
+        <v>1.136179614412533</v>
+      </c>
+      <c r="U41">
+        <v>0.1125</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>1.550793356415081</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1408090960142125</v>
+      </c>
+      <c r="C42">
+        <v>12.58227256279798</v>
+      </c>
+      <c r="D42">
+        <v>15.27787256279798</v>
+      </c>
+      <c r="E42">
+        <v>9.146599999999999</v>
+      </c>
+      <c r="F42">
+        <v>9.2356</v>
+      </c>
+      <c r="G42">
+        <v>6.54</v>
+      </c>
+      <c r="H42">
+        <v>23</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.15</v>
+      </c>
+      <c r="K42">
+        <v>0.579</v>
+      </c>
+      <c r="L42">
+        <v>1.571</v>
+      </c>
+      <c r="M42">
+        <v>1.039005</v>
+      </c>
+      <c r="N42">
+        <v>0.531995</v>
+      </c>
+      <c r="O42">
+        <v>0.13299875</v>
+      </c>
+      <c r="P42">
+        <v>0.39899625</v>
+      </c>
+      <c r="Q42">
+        <v>0.9779962499999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1784318266903542</v>
+      </c>
+      <c r="T42">
+        <v>1.151916174168939</v>
+      </c>
+      <c r="U42">
+        <v>0.1125</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>1.512023522504704</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1715214512239917</v>
+      </c>
+      <c r="C43">
+        <v>9.139851468997382</v>
+      </c>
+      <c r="D43">
+        <v>12.06634146899738</v>
+      </c>
+      <c r="E43">
+        <v>9.37749</v>
+      </c>
+      <c r="F43">
+        <v>9.46649</v>
+      </c>
+      <c r="G43">
+        <v>6.54</v>
+      </c>
+      <c r="H43">
+        <v>23</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.15</v>
+      </c>
+      <c r="K43">
+        <v>0.579</v>
+      </c>
+      <c r="L43">
+        <v>1.571</v>
+      </c>
+      <c r="M43">
+        <v>1.861111934</v>
+      </c>
+      <c r="N43">
+        <v>-0.290111934</v>
+      </c>
+      <c r="O43">
+        <v>-0.0725279835</v>
+      </c>
+      <c r="P43">
+        <v>-0.2175839505</v>
+      </c>
+      <c r="Q43">
+        <v>0.3614160494999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1829249421223214</v>
+      </c>
+      <c r="T43">
+        <v>1.188982883537203</v>
+      </c>
+      <c r="U43">
+        <v>0.1966</v>
+      </c>
+      <c r="V43">
+        <v>0.2110297574396189</v>
+      </c>
+      <c r="W43">
+        <v>0.1551115496873709</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.8441190297584755</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1730994512239917</v>
+      </c>
+      <c r="C44">
+        <v>8.780031672836614</v>
+      </c>
+      <c r="D44">
+        <v>11.93741167283661</v>
+      </c>
+      <c r="E44">
+        <v>9.608379999999999</v>
+      </c>
+      <c r="F44">
+        <v>9.697379999999999</v>
+      </c>
+      <c r="G44">
+        <v>6.54</v>
+      </c>
+      <c r="H44">
+        <v>23</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.15</v>
+      </c>
+      <c r="K44">
+        <v>0.579</v>
+      </c>
+      <c r="L44">
+        <v>1.571</v>
+      </c>
+      <c r="M44">
+        <v>1.906504908</v>
+      </c>
+      <c r="N44">
+        <v>-0.3355049079999999</v>
+      </c>
+      <c r="O44">
+        <v>-0.08387622699999997</v>
+      </c>
+      <c r="P44">
+        <v>-0.2516286809999999</v>
+      </c>
+      <c r="Q44">
+        <v>0.327371319</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1854098549175338</v>
+      </c>
+      <c r="T44">
+        <v>1.209482588425775</v>
+      </c>
+      <c r="U44">
+        <v>0.1966</v>
+      </c>
+      <c r="V44">
+        <v>0.2060052394053423</v>
+      </c>
+      <c r="W44">
+        <v>0.1560993699329097</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.8240209576213691</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1746774512239917</v>
+      </c>
+      <c r="C45">
+        <v>8.422937997641361</v>
+      </c>
+      <c r="D45">
+        <v>11.81120799764136</v>
+      </c>
+      <c r="E45">
+        <v>9.839269999999999</v>
+      </c>
+      <c r="F45">
+        <v>9.928269999999999</v>
+      </c>
+      <c r="G45">
+        <v>6.54</v>
+      </c>
+      <c r="H45">
+        <v>23</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.15</v>
+      </c>
+      <c r="K45">
+        <v>0.579</v>
+      </c>
+      <c r="L45">
+        <v>1.571</v>
+      </c>
+      <c r="M45">
+        <v>1.951897882</v>
+      </c>
+      <c r="N45">
+        <v>-0.380897882</v>
+      </c>
+      <c r="O45">
+        <v>-0.09522447049999999</v>
+      </c>
+      <c r="P45">
+        <v>-0.2856734115</v>
+      </c>
+      <c r="Q45">
+        <v>0.2933265885</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1879819576353853</v>
+      </c>
+      <c r="T45">
+        <v>1.230701581205175</v>
+      </c>
+      <c r="U45">
+        <v>0.1966</v>
+      </c>
+      <c r="V45">
+        <v>0.2012144198842878</v>
+      </c>
+      <c r="W45">
+        <v>0.157041245050749</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8048576795371511</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1844714011774938</v>
+      </c>
+      <c r="C46">
+        <v>7.464760511249143</v>
+      </c>
+      <c r="D46">
+        <v>11.08392051124914</v>
+      </c>
+      <c r="E46">
+        <v>10.07016</v>
+      </c>
+      <c r="F46">
+        <v>10.15916</v>
+      </c>
+      <c r="G46">
+        <v>6.54</v>
+      </c>
+      <c r="H46">
+        <v>23</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.15</v>
+      </c>
+      <c r="K46">
+        <v>0.579</v>
+      </c>
+      <c r="L46">
+        <v>1.571</v>
+      </c>
+      <c r="M46">
+        <v>2.172028408</v>
+      </c>
+      <c r="N46">
+        <v>-0.6010284080000001</v>
+      </c>
+      <c r="O46">
+        <v>-0.150257102</v>
+      </c>
+      <c r="P46">
+        <v>-0.4507713060000001</v>
+      </c>
+      <c r="Q46">
+        <v>0.1282286939999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1918029746529852</v>
+      </c>
+      <c r="T46">
+        <v>1.262223701975741</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.180821760228101</v>
+      </c>
+      <c r="W46">
+        <v>0.175140307663232</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.7232870409124041</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1862214011774938</v>
+      </c>
+      <c r="C47">
+        <v>7.113246676083202</v>
+      </c>
+      <c r="D47">
+        <v>10.9632966760832</v>
+      </c>
+      <c r="E47">
+        <v>10.30105</v>
+      </c>
+      <c r="F47">
+        <v>10.39005</v>
+      </c>
+      <c r="G47">
+        <v>6.54</v>
+      </c>
+      <c r="H47">
+        <v>23</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.15</v>
+      </c>
+      <c r="K47">
+        <v>0.579</v>
+      </c>
+      <c r="L47">
+        <v>1.571</v>
+      </c>
+      <c r="M47">
+        <v>2.22139269</v>
+      </c>
+      <c r="N47">
+        <v>-0.6503926900000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.1625981725</v>
+      </c>
+      <c r="P47">
+        <v>-0.4877945175000001</v>
+      </c>
+      <c r="Q47">
+        <v>0.09120548249999988</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1945848469194031</v>
+      </c>
+      <c r="T47">
+        <v>1.285173223829845</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1768034988896988</v>
+      </c>
+      <c r="W47">
+        <v>0.1759994119373824</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.707213995558795</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1879714011774938</v>
+      </c>
+      <c r="C48">
+        <v>6.764330020982834</v>
+      </c>
+      <c r="D48">
+        <v>10.84527002098283</v>
+      </c>
+      <c r="E48">
+        <v>10.53194</v>
+      </c>
+      <c r="F48">
+        <v>10.62094</v>
+      </c>
+      <c r="G48">
+        <v>6.54</v>
+      </c>
+      <c r="H48">
+        <v>23</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.15</v>
+      </c>
+      <c r="K48">
+        <v>0.579</v>
+      </c>
+      <c r="L48">
+        <v>1.571</v>
+      </c>
+      <c r="M48">
+        <v>2.270756972</v>
+      </c>
+      <c r="N48">
+        <v>-0.6997569719999996</v>
+      </c>
+      <c r="O48">
+        <v>-0.1749392429999999</v>
+      </c>
+      <c r="P48">
+        <v>-0.5248177289999998</v>
+      </c>
+      <c r="Q48">
+        <v>0.05418227100000017</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1974697514919846</v>
+      </c>
+      <c r="T48">
+        <v>1.308972727974842</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1729599445660097</v>
+      </c>
+      <c r="W48">
+        <v>0.1768211638517871</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6918397782640389</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1897214011774938</v>
+      </c>
+      <c r="C49">
+        <v>6.417927558618807</v>
+      </c>
+      <c r="D49">
+        <v>10.72975755861881</v>
+      </c>
+      <c r="E49">
+        <v>10.76283</v>
+      </c>
+      <c r="F49">
+        <v>10.85183</v>
+      </c>
+      <c r="G49">
+        <v>6.54</v>
+      </c>
+      <c r="H49">
+        <v>23</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.15</v>
+      </c>
+      <c r="K49">
+        <v>0.579</v>
+      </c>
+      <c r="L49">
+        <v>1.571</v>
+      </c>
+      <c r="M49">
+        <v>2.320121254</v>
+      </c>
+      <c r="N49">
+        <v>-0.7491212540000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.1872803135</v>
+      </c>
+      <c r="P49">
+        <v>-0.5618409405</v>
+      </c>
+      <c r="Q49">
+        <v>0.01715905949999996</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2004635203880598</v>
+      </c>
+      <c r="T49">
+        <v>1.333670326615877</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1692799457454563</v>
+      </c>
+      <c r="W49">
+        <v>0.1776079475996215</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6771197829818252</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1914714011774938</v>
+      </c>
+      <c r="C50">
+        <v>6.073959799978113</v>
+      </c>
+      <c r="D50">
+        <v>10.61667979997811</v>
+      </c>
+      <c r="E50">
+        <v>10.99372</v>
+      </c>
+      <c r="F50">
+        <v>11.08272</v>
+      </c>
+      <c r="G50">
+        <v>6.54</v>
+      </c>
+      <c r="H50">
+        <v>23</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.15</v>
+      </c>
+      <c r="K50">
+        <v>0.579</v>
+      </c>
+      <c r="L50">
+        <v>1.571</v>
+      </c>
+      <c r="M50">
+        <v>2.369485536</v>
+      </c>
+      <c r="N50">
+        <v>-0.7984855359999996</v>
+      </c>
+      <c r="O50">
+        <v>-0.1996213839999999</v>
+      </c>
+      <c r="P50">
+        <v>-0.5988641519999998</v>
+      </c>
+      <c r="Q50">
+        <v>-0.0198641519999998</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2035724342416763</v>
+      </c>
+      <c r="T50">
+        <v>1.359317832896952</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1657532802090926</v>
+      </c>
+      <c r="W50">
+        <v>0.178361948691296</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6630131208363705</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1932214011774938</v>
+      </c>
+      <c r="C51">
+        <v>5.732350571947732</v>
+      </c>
+      <c r="D51">
+        <v>10.50596057194773</v>
+      </c>
+      <c r="E51">
+        <v>11.22461</v>
+      </c>
+      <c r="F51">
+        <v>11.31361</v>
+      </c>
+      <c r="G51">
+        <v>6.54</v>
+      </c>
+      <c r="H51">
+        <v>23</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.15</v>
+      </c>
+      <c r="K51">
+        <v>0.579</v>
+      </c>
+      <c r="L51">
+        <v>1.571</v>
+      </c>
+      <c r="M51">
+        <v>2.418849818</v>
+      </c>
+      <c r="N51">
+        <v>-0.8478498179999996</v>
+      </c>
+      <c r="O51">
+        <v>-0.2119624544999999</v>
+      </c>
+      <c r="P51">
+        <v>-0.6358873634999997</v>
+      </c>
+      <c r="Q51">
+        <v>-0.05688736349999979</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2068032662856308</v>
+      </c>
+      <c r="T51">
+        <v>1.385971123738068</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1623705602048254</v>
+      </c>
+      <c r="W51">
+        <v>0.1790851742282083</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6494822408193017</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1949714011774938</v>
+      </c>
+      <c r="C52">
+        <v>5.39302684619496</v>
+      </c>
+      <c r="D52">
+        <v>10.39752684619496</v>
+      </c>
+      <c r="E52">
+        <v>11.4555</v>
+      </c>
+      <c r="F52">
+        <v>11.5445</v>
+      </c>
+      <c r="G52">
+        <v>6.54</v>
+      </c>
+      <c r="H52">
+        <v>23</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.15</v>
+      </c>
+      <c r="K52">
+        <v>0.579</v>
+      </c>
+      <c r="L52">
+        <v>1.571</v>
+      </c>
+      <c r="M52">
+        <v>2.4682141</v>
+      </c>
+      <c r="N52">
+        <v>-0.8972140999999996</v>
+      </c>
+      <c r="O52">
+        <v>-0.2243035249999999</v>
+      </c>
+      <c r="P52">
+        <v>-0.6729105749999997</v>
+      </c>
+      <c r="Q52">
+        <v>-0.09391057499999977</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2101633316113434</v>
+      </c>
+      <c r="T52">
+        <v>1.41369054621283</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1591231490007289</v>
+      </c>
+      <c r="W52">
+        <v>0.1797794707436441</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6364925960029157</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1967214011774938</v>
+      </c>
+      <c r="C53">
+        <v>5.055918578536327</v>
+      </c>
+      <c r="D53">
+        <v>10.29130857853633</v>
+      </c>
+      <c r="E53">
+        <v>11.68639</v>
+      </c>
+      <c r="F53">
+        <v>11.77539</v>
+      </c>
+      <c r="G53">
+        <v>6.54</v>
+      </c>
+      <c r="H53">
+        <v>23</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.15</v>
+      </c>
+      <c r="K53">
+        <v>0.579</v>
+      </c>
+      <c r="L53">
+        <v>1.571</v>
+      </c>
+      <c r="M53">
+        <v>2.517578382</v>
+      </c>
+      <c r="N53">
+        <v>-0.946578382</v>
+      </c>
+      <c r="O53">
+        <v>-0.2366445955</v>
+      </c>
+      <c r="P53">
+        <v>-0.7099337864999999</v>
+      </c>
+      <c r="Q53">
+        <v>-0.1309337865</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2136605424605545</v>
+      </c>
+      <c r="T53">
+        <v>1.442541373686561</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1560030872556166</v>
+      </c>
+      <c r="W53">
+        <v>0.1804465399447492</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.6240123490224663</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1984714011774938</v>
+      </c>
+      <c r="C54">
+        <v>4.7209585580528</v>
+      </c>
+      <c r="D54">
+        <v>10.1872385580528</v>
+      </c>
+      <c r="E54">
+        <v>11.91728</v>
+      </c>
+      <c r="F54">
+        <v>12.00628</v>
+      </c>
+      <c r="G54">
+        <v>6.54</v>
+      </c>
+      <c r="H54">
+        <v>23</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.15</v>
+      </c>
+      <c r="K54">
+        <v>0.579</v>
+      </c>
+      <c r="L54">
+        <v>1.571</v>
+      </c>
+      <c r="M54">
+        <v>2.566942664</v>
+      </c>
+      <c r="N54">
+        <v>-0.995942664</v>
+      </c>
+      <c r="O54">
+        <v>-0.248985666</v>
+      </c>
+      <c r="P54">
+        <v>-0.7469569979999999</v>
+      </c>
+      <c r="Q54">
+        <v>-0.167956998</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2173034704284828</v>
+      </c>
+      <c r="T54">
+        <v>1.472594318971698</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1530030278853163</v>
+      </c>
+      <c r="W54">
+        <v>0.1810879526381194</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.612012111541265</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2002214011774938</v>
+      </c>
+      <c r="C55">
+        <v>4.388082265268123</v>
+      </c>
+      <c r="D55">
+        <v>10.08525226526812</v>
+      </c>
+      <c r="E55">
+        <v>12.14817</v>
+      </c>
+      <c r="F55">
+        <v>12.23717</v>
+      </c>
+      <c r="G55">
+        <v>6.54</v>
+      </c>
+      <c r="H55">
+        <v>23</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.15</v>
+      </c>
+      <c r="K55">
+        <v>0.579</v>
+      </c>
+      <c r="L55">
+        <v>1.571</v>
+      </c>
+      <c r="M55">
+        <v>2.616306946</v>
+      </c>
+      <c r="N55">
+        <v>-1.045306946</v>
+      </c>
+      <c r="O55">
+        <v>-0.2613267365</v>
+      </c>
+      <c r="P55">
+        <v>-0.7839802094999999</v>
+      </c>
+      <c r="Q55">
+        <v>-0.2049802095</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2211014166078122</v>
+      </c>
+      <c r="T55">
+        <v>1.503926112992372</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1501161783025745</v>
+      </c>
+      <c r="W55">
+        <v>0.1817051610789096</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.6004647132102978</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2019714011774938</v>
+      </c>
+      <c r="C56">
+        <v>4.05722773876162</v>
+      </c>
+      <c r="D56">
+        <v>9.985287738761619</v>
+      </c>
+      <c r="E56">
+        <v>12.37906</v>
+      </c>
+      <c r="F56">
+        <v>12.46806</v>
+      </c>
+      <c r="G56">
+        <v>6.54</v>
+      </c>
+      <c r="H56">
+        <v>23</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.15</v>
+      </c>
+      <c r="K56">
+        <v>0.579</v>
+      </c>
+      <c r="L56">
+        <v>1.571</v>
+      </c>
+      <c r="M56">
+        <v>2.665671228</v>
+      </c>
+      <c r="N56">
+        <v>-1.094671228</v>
+      </c>
+      <c r="O56">
+        <v>-0.273667807</v>
+      </c>
+      <c r="P56">
+        <v>-0.8210034209999999</v>
+      </c>
+      <c r="Q56">
+        <v>-0.2420034209999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.225064490881895</v>
+      </c>
+      <c r="T56">
+        <v>1.536620158926989</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.147336249074749</v>
+      </c>
+      <c r="W56">
+        <v>0.1822995099478187</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5893449962989959</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2037214011774938</v>
+      </c>
+      <c r="C57">
+        <v>3.728335449635814</v>
+      </c>
+      <c r="D57">
+        <v>9.887285449635813</v>
+      </c>
+      <c r="E57">
+        <v>12.60995</v>
+      </c>
+      <c r="F57">
+        <v>12.69895</v>
+      </c>
+      <c r="G57">
+        <v>6.54</v>
+      </c>
+      <c r="H57">
+        <v>23</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.15</v>
+      </c>
+      <c r="K57">
+        <v>0.579</v>
+      </c>
+      <c r="L57">
+        <v>1.571</v>
+      </c>
+      <c r="M57">
+        <v>2.71503551</v>
+      </c>
+      <c r="N57">
+        <v>-1.14403551</v>
+      </c>
+      <c r="O57">
+        <v>-0.2860088775</v>
+      </c>
+      <c r="P57">
+        <v>-0.8580266324999999</v>
+      </c>
+      <c r="Q57">
+        <v>-0.2790266324999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2292037017903816</v>
+      </c>
+      <c r="T57">
+        <v>1.570767273569811</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1446574081824808</v>
+      </c>
+      <c r="W57">
+        <v>0.1828722461305856</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5786296327299233</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2054714011774938</v>
+      </c>
+      <c r="C58">
+        <v>3.401348183304615</v>
+      </c>
+      <c r="D58">
+        <v>9.791188183304616</v>
+      </c>
+      <c r="E58">
+        <v>12.84084</v>
+      </c>
+      <c r="F58">
+        <v>12.92984</v>
+      </c>
+      <c r="G58">
+        <v>6.54</v>
+      </c>
+      <c r="H58">
+        <v>23</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.15</v>
+      </c>
+      <c r="K58">
+        <v>0.579</v>
+      </c>
+      <c r="L58">
+        <v>1.571</v>
+      </c>
+      <c r="M58">
+        <v>2.764399792</v>
+      </c>
+      <c r="N58">
+        <v>-1.193399792</v>
+      </c>
+      <c r="O58">
+        <v>-0.298349948</v>
+      </c>
+      <c r="P58">
+        <v>-0.8950498439999999</v>
+      </c>
+      <c r="Q58">
+        <v>-0.3160498439999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2335310586492539</v>
+      </c>
+      <c r="T58">
+        <v>1.606466529787307</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1420742401792222</v>
+      </c>
+      <c r="W58">
+        <v>0.1834245274496823</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.568296960716889</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2072214011774938</v>
+      </c>
+      <c r="C59">
+        <v>3.076210928108736</v>
+      </c>
+      <c r="D59">
+        <v>9.696940928108736</v>
+      </c>
+      <c r="E59">
+        <v>13.07173</v>
+      </c>
+      <c r="F59">
+        <v>13.16073</v>
+      </c>
+      <c r="G59">
+        <v>6.54</v>
+      </c>
+      <c r="H59">
+        <v>23</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.15</v>
+      </c>
+      <c r="K59">
+        <v>0.579</v>
+      </c>
+      <c r="L59">
+        <v>1.571</v>
+      </c>
+      <c r="M59">
+        <v>2.813764074</v>
+      </c>
+      <c r="N59">
+        <v>-1.242764074</v>
+      </c>
+      <c r="O59">
+        <v>-0.3106910185000001</v>
+      </c>
+      <c r="P59">
+        <v>-0.9320730555000003</v>
+      </c>
+      <c r="Q59">
+        <v>-0.3530730555000003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2380596879201668</v>
+      </c>
+      <c r="T59">
+        <v>1.643826216526547</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1395817096497622</v>
+      </c>
+      <c r="W59">
+        <v>0.1839574304768808</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5583268385990487</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2089714011774938</v>
+      </c>
+      <c r="C60">
+        <v>2.752870770302694</v>
+      </c>
+      <c r="D60">
+        <v>9.604490770302691</v>
+      </c>
+      <c r="E60">
+        <v>13.30262</v>
+      </c>
+      <c r="F60">
+        <v>13.39162</v>
+      </c>
+      <c r="G60">
+        <v>6.54</v>
+      </c>
+      <c r="H60">
+        <v>23</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.15</v>
+      </c>
+      <c r="K60">
+        <v>0.579</v>
+      </c>
+      <c r="L60">
+        <v>1.571</v>
+      </c>
+      <c r="M60">
+        <v>2.863128355999999</v>
+      </c>
+      <c r="N60">
+        <v>-1.292128355999999</v>
+      </c>
+      <c r="O60">
+        <v>-0.3230320889999999</v>
+      </c>
+      <c r="P60">
+        <v>-0.9690962669999996</v>
+      </c>
+      <c r="Q60">
+        <v>-0.3900962669999997</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2428039662039803</v>
+      </c>
+      <c r="T60">
+        <v>1.682964935967655</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1371751284489043</v>
+      </c>
+      <c r="W60">
+        <v>0.1844719575376243</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.548700513795617</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2107214011774938</v>
+      </c>
+      <c r="C61">
+        <v>2.43127679499224</v>
+      </c>
+      <c r="D61">
+        <v>9.513786794992239</v>
+      </c>
+      <c r="E61">
+        <v>13.53351</v>
+      </c>
+      <c r="F61">
+        <v>13.62251</v>
+      </c>
+      <c r="G61">
+        <v>6.54</v>
+      </c>
+      <c r="H61">
+        <v>23</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.15</v>
+      </c>
+      <c r="K61">
+        <v>0.579</v>
+      </c>
+      <c r="L61">
+        <v>1.571</v>
+      </c>
+      <c r="M61">
+        <v>2.912492637999999</v>
+      </c>
+      <c r="N61">
+        <v>-1.341492637999999</v>
+      </c>
+      <c r="O61">
+        <v>-0.3353731594999999</v>
+      </c>
+      <c r="P61">
+        <v>-1.0061194785</v>
+      </c>
+      <c r="Q61">
+        <v>-0.4271194784999996</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2477796726967602</v>
+      </c>
+      <c r="T61">
+        <v>1.724012861235158</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1348501262718042</v>
+      </c>
+      <c r="W61">
+        <v>0.1849690430030883</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5394005050872168</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2124714011774938</v>
+      </c>
+      <c r="C62">
+        <v>2.111379992632509</v>
+      </c>
+      <c r="D62">
+        <v>9.424779992632507</v>
+      </c>
+      <c r="E62">
+        <v>13.7644</v>
+      </c>
+      <c r="F62">
+        <v>13.8534</v>
+      </c>
+      <c r="G62">
+        <v>6.54</v>
+      </c>
+      <c r="H62">
+        <v>23</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.15</v>
+      </c>
+      <c r="K62">
+        <v>0.579</v>
+      </c>
+      <c r="L62">
+        <v>1.571</v>
+      </c>
+      <c r="M62">
+        <v>2.96185692</v>
+      </c>
+      <c r="N62">
+        <v>-1.39085692</v>
+      </c>
+      <c r="O62">
+        <v>-0.34771423</v>
+      </c>
+      <c r="P62">
+        <v>-1.04314269</v>
+      </c>
+      <c r="Q62">
+        <v>-0.4641426899999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2530041645141793</v>
+      </c>
+      <c r="T62">
+        <v>1.767113182766037</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1326026241672741</v>
+      </c>
+      <c r="W62">
+        <v>0.1854495589530368</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5304104966690963</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2142214011774938</v>
+      </c>
+      <c r="C63">
+        <v>1.793133170726069</v>
+      </c>
+      <c r="D63">
+        <v>9.337423170726067</v>
+      </c>
+      <c r="E63">
+        <v>13.99529</v>
+      </c>
+      <c r="F63">
+        <v>14.08429</v>
+      </c>
+      <c r="G63">
+        <v>6.54</v>
+      </c>
+      <c r="H63">
+        <v>23</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.15</v>
+      </c>
+      <c r="K63">
+        <v>0.579</v>
+      </c>
+      <c r="L63">
+        <v>1.571</v>
+      </c>
+      <c r="M63">
+        <v>3.011221202</v>
+      </c>
+      <c r="N63">
+        <v>-1.440221202</v>
+      </c>
+      <c r="O63">
+        <v>-0.3600553005</v>
+      </c>
+      <c r="P63">
+        <v>-1.0801659015</v>
+      </c>
+      <c r="Q63">
+        <v>-0.5011659014999998</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2584965789889018</v>
+      </c>
+      <c r="T63">
+        <v>1.812423777195936</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1304288106563352</v>
+      </c>
+      <c r="W63">
+        <v>0.1859143202816755</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5217152426253406</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2159714011774938</v>
+      </c>
+      <c r="C64">
+        <v>1.476490870386625</v>
+      </c>
+      <c r="D64">
+        <v>9.251670870386624</v>
+      </c>
+      <c r="E64">
+        <v>14.22618</v>
+      </c>
+      <c r="F64">
+        <v>14.31518</v>
+      </c>
+      <c r="G64">
+        <v>6.54</v>
+      </c>
+      <c r="H64">
+        <v>23</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.15</v>
+      </c>
+      <c r="K64">
+        <v>0.579</v>
+      </c>
+      <c r="L64">
+        <v>1.571</v>
+      </c>
+      <c r="M64">
+        <v>3.060585484</v>
+      </c>
+      <c r="N64">
+        <v>-1.489585484</v>
+      </c>
+      <c r="O64">
+        <v>-0.3723963709999999</v>
+      </c>
+      <c r="P64">
+        <v>-1.117189113</v>
+      </c>
+      <c r="Q64">
+        <v>-0.5381891129999998</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2642780679096624</v>
+      </c>
+      <c r="T64">
+        <v>1.860119139753723</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.1283251201618782</v>
+      </c>
+      <c r="W64">
+        <v>0.1863640893093904</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5133004806475127</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2177214011774938</v>
+      </c>
+      <c r="C65">
+        <v>1.161409287458445</v>
+      </c>
+      <c r="D65">
+        <v>9.167479287458443</v>
+      </c>
+      <c r="E65">
+        <v>14.45707</v>
+      </c>
+      <c r="F65">
+        <v>14.54607</v>
+      </c>
+      <c r="G65">
+        <v>6.54</v>
+      </c>
+      <c r="H65">
+        <v>23</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.15</v>
+      </c>
+      <c r="K65">
+        <v>0.579</v>
+      </c>
+      <c r="L65">
+        <v>1.571</v>
+      </c>
+      <c r="M65">
+        <v>3.109949766</v>
+      </c>
+      <c r="N65">
+        <v>-1.538949766</v>
+      </c>
+      <c r="O65">
+        <v>-0.3847374414999999</v>
+      </c>
+      <c r="P65">
+        <v>-1.1542123245</v>
+      </c>
+      <c r="Q65">
+        <v>-0.5752123244999998</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2703720697450587</v>
+      </c>
+      <c r="T65">
+        <v>1.910392630017338</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.126288213492642</v>
+      </c>
+      <c r="W65">
+        <v>0.1867995799552731</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.505152853970568</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.236246759076841</v>
+      </c>
+      <c r="C66">
+        <v>0.1249844333631884</v>
+      </c>
+      <c r="D66">
+        <v>8.361944433363188</v>
+      </c>
+      <c r="E66">
+        <v>14.68796</v>
+      </c>
+      <c r="F66">
+        <v>14.77696</v>
+      </c>
+      <c r="G66">
+        <v>6.54</v>
+      </c>
+      <c r="H66">
+        <v>23</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.15</v>
+      </c>
+      <c r="K66">
+        <v>0.579</v>
+      </c>
+      <c r="L66">
+        <v>1.571</v>
+      </c>
+      <c r="M66">
+        <v>3.528738048</v>
+      </c>
+      <c r="N66">
+        <v>-1.957738048</v>
+      </c>
+      <c r="O66">
+        <v>-0.489434512</v>
+      </c>
+      <c r="P66">
+        <v>-1.468303536</v>
+      </c>
+      <c r="Q66">
+        <v>-0.8893035360000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2789583991806081</v>
+      </c>
+      <c r="T66">
+        <v>1.981226994846538</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.1113004124017085</v>
+      </c>
+      <c r="W66">
+        <v>0.212221461518472</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4452016496068342</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.238246759076841</v>
+      </c>
+      <c r="C67">
+        <v>-0.184484228102674</v>
+      </c>
+      <c r="D67">
+        <v>8.283365771897325</v>
+      </c>
+      <c r="E67">
+        <v>14.91885</v>
+      </c>
+      <c r="F67">
+        <v>15.00785</v>
+      </c>
+      <c r="G67">
+        <v>6.54</v>
+      </c>
+      <c r="H67">
+        <v>23</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.15</v>
+      </c>
+      <c r="K67">
+        <v>0.579</v>
+      </c>
+      <c r="L67">
+        <v>1.571</v>
+      </c>
+      <c r="M67">
+        <v>3.58387458</v>
+      </c>
+      <c r="N67">
+        <v>-2.01287458</v>
+      </c>
+      <c r="O67">
+        <v>-0.503218645</v>
+      </c>
+      <c r="P67">
+        <v>-1.509655935</v>
+      </c>
+      <c r="Q67">
+        <v>-0.9306559350000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2858200677286256</v>
+      </c>
+      <c r="T67">
+        <v>2.037833480413582</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.1095880983647592</v>
+      </c>
+      <c r="W67">
+        <v>0.2126303621104955</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4383523934590368</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.240246759076841</v>
+      </c>
+      <c r="C68">
+        <v>-0.4924898034615772</v>
+      </c>
+      <c r="D68">
+        <v>8.206250196538424</v>
+      </c>
+      <c r="E68">
+        <v>15.14974</v>
+      </c>
+      <c r="F68">
+        <v>15.23874</v>
+      </c>
+      <c r="G68">
+        <v>6.54</v>
+      </c>
+      <c r="H68">
+        <v>23</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.15</v>
+      </c>
+      <c r="K68">
+        <v>0.579</v>
+      </c>
+      <c r="L68">
+        <v>1.571</v>
+      </c>
+      <c r="M68">
+        <v>3.639011112</v>
+      </c>
+      <c r="N68">
+        <v>-2.068011112000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.5170027780000002</v>
+      </c>
+      <c r="P68">
+        <v>-1.551008334</v>
+      </c>
+      <c r="Q68">
+        <v>-0.9720083340000005</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2930853638382909</v>
+      </c>
+      <c r="T68">
+        <v>2.097769759249275</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.1079276726319598</v>
+      </c>
+      <c r="W68">
+        <v>0.213026871775488</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4317106905278391</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.242246759076841</v>
+      </c>
+      <c r="C69">
+        <v>-0.799072778442353</v>
+      </c>
+      <c r="D69">
+        <v>8.130557221557646</v>
+      </c>
+      <c r="E69">
+        <v>15.38063</v>
+      </c>
+      <c r="F69">
+        <v>15.46963</v>
+      </c>
+      <c r="G69">
+        <v>6.54</v>
+      </c>
+      <c r="H69">
+        <v>23</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.15</v>
+      </c>
+      <c r="K69">
+        <v>0.579</v>
+      </c>
+      <c r="L69">
+        <v>1.571</v>
+      </c>
+      <c r="M69">
+        <v>3.694147644000001</v>
+      </c>
+      <c r="N69">
+        <v>-2.123147644</v>
+      </c>
+      <c r="O69">
+        <v>-0.5307869110000001</v>
+      </c>
+      <c r="P69">
+        <v>-1.592360733</v>
+      </c>
+      <c r="Q69">
+        <v>-1.013360733</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3007909809242997</v>
+      </c>
+      <c r="T69">
+        <v>2.161338539832587</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.1063168118464081</v>
+      </c>
+      <c r="W69">
+        <v>0.2134115453310777</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4252672473856326</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.244246759076841</v>
+      </c>
+      <c r="C70">
+        <v>-1.104272158693551</v>
+      </c>
+      <c r="D70">
+        <v>8.056247841306451</v>
+      </c>
+      <c r="E70">
+        <v>15.61152</v>
+      </c>
+      <c r="F70">
+        <v>15.70052</v>
+      </c>
+      <c r="G70">
+        <v>6.54</v>
+      </c>
+      <c r="H70">
+        <v>23</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.15</v>
+      </c>
+      <c r="K70">
+        <v>0.579</v>
+      </c>
+      <c r="L70">
+        <v>1.571</v>
+      </c>
+      <c r="M70">
+        <v>3.749284176</v>
+      </c>
+      <c r="N70">
+        <v>-2.178284176</v>
+      </c>
+      <c r="O70">
+        <v>-0.544571044</v>
+      </c>
+      <c r="P70">
+        <v>-1.633713132</v>
+      </c>
+      <c r="Q70">
+        <v>-1.054713132</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3089781990781842</v>
+      </c>
+      <c r="T70">
+        <v>2.228880369202356</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.1047533293192551</v>
+      </c>
+      <c r="W70">
+        <v>0.2137849049585619</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.4190133172770204</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.246246759076841</v>
+      </c>
+      <c r="C71">
+        <v>-1.40812553680691</v>
+      </c>
+      <c r="D71">
+        <v>7.98328446319309</v>
+      </c>
+      <c r="E71">
+        <v>15.84241</v>
+      </c>
+      <c r="F71">
+        <v>15.93141</v>
+      </c>
+      <c r="G71">
+        <v>6.54</v>
+      </c>
+      <c r="H71">
+        <v>23</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.15</v>
+      </c>
+      <c r="K71">
+        <v>0.579</v>
+      </c>
+      <c r="L71">
+        <v>1.571</v>
+      </c>
+      <c r="M71">
+        <v>3.804420708</v>
+      </c>
+      <c r="N71">
+        <v>-2.233420708000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.5583551770000001</v>
+      </c>
+      <c r="P71">
+        <v>-1.675065531</v>
+      </c>
+      <c r="Q71">
+        <v>-1.096065531</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3176936248548998</v>
+      </c>
+      <c r="T71">
+        <v>2.300779735950818</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.1032351651262224</v>
+      </c>
+      <c r="W71">
+        <v>0.2141474425678581</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.4129406605048895</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.248246759076841</v>
+      </c>
+      <c r="C72">
+        <v>-1.710669155731585</v>
+      </c>
+      <c r="D72">
+        <v>7.911630844268417</v>
+      </c>
+      <c r="E72">
+        <v>16.0733</v>
+      </c>
+      <c r="F72">
+        <v>16.1623</v>
+      </c>
+      <c r="G72">
+        <v>6.54</v>
+      </c>
+      <c r="H72">
+        <v>23</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.15</v>
+      </c>
+      <c r="K72">
+        <v>0.579</v>
+      </c>
+      <c r="L72">
+        <v>1.571</v>
+      </c>
+      <c r="M72">
+        <v>3.85955724</v>
+      </c>
+      <c r="N72">
+        <v>-2.28855724</v>
+      </c>
+      <c r="O72">
+        <v>-0.5721393100000001</v>
+      </c>
+      <c r="P72">
+        <v>-1.71641793</v>
+      </c>
+      <c r="Q72">
+        <v>-1.13741793</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3269900790167298</v>
+      </c>
+      <c r="T72">
+        <v>2.377472393815846</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.1017603770529907</v>
+      </c>
+      <c r="W72">
+        <v>0.2144996219597458</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4070415082119627</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.250246759076841</v>
+      </c>
+      <c r="C73">
+        <v>-2.011937968803581</v>
+      </c>
+      <c r="D73">
+        <v>7.841252031196416</v>
+      </c>
+      <c r="E73">
+        <v>16.30419</v>
+      </c>
+      <c r="F73">
+        <v>16.39319</v>
+      </c>
+      <c r="G73">
+        <v>6.54</v>
+      </c>
+      <c r="H73">
+        <v>23</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.15</v>
+      </c>
+      <c r="K73">
+        <v>0.579</v>
+      </c>
+      <c r="L73">
+        <v>1.571</v>
+      </c>
+      <c r="M73">
+        <v>3.914693772</v>
+      </c>
+      <c r="N73">
+        <v>-2.343693772</v>
+      </c>
+      <c r="O73">
+        <v>-0.585923443</v>
+      </c>
+      <c r="P73">
+        <v>-1.757770329</v>
+      </c>
+      <c r="Q73">
+        <v>-1.178770329</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3369276679483411</v>
+      </c>
+      <c r="T73">
+        <v>2.45945420049915</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.1003271323057655</v>
+      </c>
+      <c r="W73">
+        <v>0.2148418808053832</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4013085292230617</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.252246759076841</v>
+      </c>
+      <c r="C74">
+        <v>-2.311965696599554</v>
+      </c>
+      <c r="D74">
+        <v>7.772114303400445</v>
+      </c>
+      <c r="E74">
+        <v>16.53508</v>
+      </c>
+      <c r="F74">
+        <v>16.62408</v>
+      </c>
+      <c r="G74">
+        <v>6.54</v>
+      </c>
+      <c r="H74">
+        <v>23</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.15</v>
+      </c>
+      <c r="K74">
+        <v>0.579</v>
+      </c>
+      <c r="L74">
+        <v>1.571</v>
+      </c>
+      <c r="M74">
+        <v>3.969830304</v>
+      </c>
+      <c r="N74">
+        <v>-2.398830304000001</v>
+      </c>
+      <c r="O74">
+        <v>-0.5997075760000001</v>
+      </c>
+      <c r="P74">
+        <v>-1.799122728</v>
+      </c>
+      <c r="Q74">
+        <v>-1.220122728</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3475750846607819</v>
+      </c>
+      <c r="T74">
+        <v>2.547291850516977</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.09893369991262981</v>
+      </c>
+      <c r="W74">
+        <v>0.215174632460864</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3957347996505192</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.254246759076841</v>
+      </c>
+      <c r="C75">
+        <v>-2.610784880809071</v>
+      </c>
+      <c r="D75">
+        <v>7.704185119190927</v>
+      </c>
+      <c r="E75">
+        <v>16.76597</v>
+      </c>
+      <c r="F75">
+        <v>16.85497</v>
+      </c>
+      <c r="G75">
+        <v>6.54</v>
+      </c>
+      <c r="H75">
+        <v>23</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.15</v>
+      </c>
+      <c r="K75">
+        <v>0.579</v>
+      </c>
+      <c r="L75">
+        <v>1.571</v>
+      </c>
+      <c r="M75">
+        <v>4.024966836</v>
+      </c>
+      <c r="N75">
+        <v>-2.453966836</v>
+      </c>
+      <c r="O75">
+        <v>-0.6134917090000001</v>
+      </c>
+      <c r="P75">
+        <v>-1.840475127</v>
+      </c>
+      <c r="Q75">
+        <v>-1.261475127</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3590111989074774</v>
+      </c>
+      <c r="T75">
+        <v>2.641635993128717</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.09757844374944311</v>
+      </c>
+      <c r="W75">
+        <v>0.215498267632633</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3903137749977724</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.256246759076841</v>
+      </c>
+      <c r="C76">
+        <v>-2.90842693530632</v>
+      </c>
+      <c r="D76">
+        <v>7.63743306469368</v>
+      </c>
+      <c r="E76">
+        <v>16.99686</v>
+      </c>
+      <c r="F76">
+        <v>17.08586</v>
+      </c>
+      <c r="G76">
+        <v>6.54</v>
+      </c>
+      <c r="H76">
+        <v>23</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.15</v>
+      </c>
+      <c r="K76">
+        <v>0.579</v>
+      </c>
+      <c r="L76">
+        <v>1.571</v>
+      </c>
+      <c r="M76">
+        <v>4.080103368000001</v>
+      </c>
+      <c r="N76">
+        <v>-2.509103368000001</v>
+      </c>
+      <c r="O76">
+        <v>-0.6272758420000002</v>
+      </c>
+      <c r="P76">
+        <v>-1.881827526000001</v>
+      </c>
+      <c r="Q76">
+        <v>-1.302827526000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3713270142500727</v>
+      </c>
+      <c r="T76">
+        <v>2.743237377479821</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.09625981613120738</v>
+      </c>
+      <c r="W76">
+        <v>0.2158131559078677</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3850392645248294</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.258246759076841</v>
+      </c>
+      <c r="C77">
+        <v>-3.204922194589553</v>
+      </c>
+      <c r="D77">
+        <v>7.571827805410446</v>
+      </c>
+      <c r="E77">
+        <v>17.22775</v>
+      </c>
+      <c r="F77">
+        <v>17.31675</v>
+      </c>
+      <c r="G77">
+        <v>6.54</v>
+      </c>
+      <c r="H77">
+        <v>23</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.15</v>
+      </c>
+      <c r="K77">
+        <v>0.579</v>
+      </c>
+      <c r="L77">
+        <v>1.571</v>
+      </c>
+      <c r="M77">
+        <v>4.1352399</v>
+      </c>
+      <c r="N77">
+        <v>-2.5642399</v>
+      </c>
+      <c r="O77">
+        <v>-0.6410599750000001</v>
+      </c>
+      <c r="P77">
+        <v>-1.923179925</v>
+      </c>
+      <c r="Q77">
+        <v>-1.344179925</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3846280948200756</v>
+      </c>
+      <c r="T77">
+        <v>2.852966872579014</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.09497635191612462</v>
+      </c>
+      <c r="W77">
+        <v>0.2161196471624295</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3799054076644984</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.260246759076841</v>
+      </c>
+      <c r="C78">
+        <v>-3.500299959745247</v>
+      </c>
+      <c r="D78">
+        <v>7.507340040254751</v>
+      </c>
+      <c r="E78">
+        <v>17.45864</v>
+      </c>
+      <c r="F78">
+        <v>17.54764</v>
+      </c>
+      <c r="G78">
+        <v>6.54</v>
+      </c>
+      <c r="H78">
+        <v>23</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.15</v>
+      </c>
+      <c r="K78">
+        <v>0.579</v>
+      </c>
+      <c r="L78">
+        <v>1.571</v>
+      </c>
+      <c r="M78">
+        <v>4.190376432</v>
+      </c>
+      <c r="N78">
+        <v>-2.619376432</v>
+      </c>
+      <c r="O78">
+        <v>-0.654844108</v>
+      </c>
+      <c r="P78">
+        <v>-1.964532324</v>
+      </c>
+      <c r="Q78">
+        <v>-1.385532324</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3990375987709122</v>
+      </c>
+      <c r="T78">
+        <v>2.971840492269807</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.09372666307512298</v>
+      </c>
+      <c r="W78">
+        <v>0.2164180728576606</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3749066523004919</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.262246759076841</v>
+      </c>
+      <c r="C79">
+        <v>-3.794588542083304</v>
+      </c>
+      <c r="D79">
+        <v>7.443941457916697</v>
+      </c>
+      <c r="E79">
+        <v>17.68953</v>
+      </c>
+      <c r="F79">
+        <v>17.77853</v>
+      </c>
+      <c r="G79">
+        <v>6.54</v>
+      </c>
+      <c r="H79">
+        <v>23</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.15</v>
+      </c>
+      <c r="K79">
+        <v>0.579</v>
+      </c>
+      <c r="L79">
+        <v>1.571</v>
+      </c>
+      <c r="M79">
+        <v>4.245512964</v>
+      </c>
+      <c r="N79">
+        <v>-2.674512964000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.6686282410000002</v>
+      </c>
+      <c r="P79">
+        <v>-2.005884723</v>
+      </c>
+      <c r="Q79">
+        <v>-1.426884723</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4147001030652996</v>
+      </c>
+      <c r="T79">
+        <v>3.10105094845545</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.09250943368453696</v>
+      </c>
+      <c r="W79">
+        <v>0.2167087472361326</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3700377347381478</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.264246759076841</v>
+      </c>
+      <c r="C80">
+        <v>-4.087815304579767</v>
+      </c>
+      <c r="D80">
+        <v>7.381604695420232</v>
+      </c>
+      <c r="E80">
+        <v>17.92042</v>
+      </c>
+      <c r="F80">
+        <v>18.00942</v>
+      </c>
+      <c r="G80">
+        <v>6.54</v>
+      </c>
+      <c r="H80">
+        <v>23</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.15</v>
+      </c>
+      <c r="K80">
+        <v>0.579</v>
+      </c>
+      <c r="L80">
+        <v>1.571</v>
+      </c>
+      <c r="M80">
+        <v>4.300649496</v>
+      </c>
+      <c r="N80">
+        <v>-2.729649496</v>
+      </c>
+      <c r="O80">
+        <v>-0.6824123740000001</v>
+      </c>
+      <c r="P80">
+        <v>-2.047237122</v>
+      </c>
+      <c r="Q80">
+        <v>-1.468237122</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4317864713864497</v>
+      </c>
+      <c r="T80">
+        <v>3.24200780974888</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.09132341530396598</v>
+      </c>
+      <c r="W80">
+        <v>0.2169919684254129</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3652936612158638</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.266246759076841</v>
+      </c>
+      <c r="C81">
+        <v>-4.380006701254599</v>
+      </c>
+      <c r="D81">
+        <v>7.320303298745402</v>
+      </c>
+      <c r="E81">
+        <v>18.15131</v>
+      </c>
+      <c r="F81">
+        <v>18.24031</v>
+      </c>
+      <c r="G81">
+        <v>6.54</v>
+      </c>
+      <c r="H81">
+        <v>23</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.15</v>
+      </c>
+      <c r="K81">
+        <v>0.579</v>
+      </c>
+      <c r="L81">
+        <v>1.571</v>
+      </c>
+      <c r="M81">
+        <v>4.355786028000001</v>
+      </c>
+      <c r="N81">
+        <v>-2.784786028000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.6961965070000002</v>
+      </c>
+      <c r="P81">
+        <v>-2.088589521000001</v>
+      </c>
+      <c r="Q81">
+        <v>-1.509589521000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4505001128810425</v>
+      </c>
+      <c r="T81">
+        <v>3.396389134022637</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.09016742270518159</v>
+      </c>
+      <c r="W81">
+        <v>0.2172680194580026</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3606696908207263</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.268246759076841</v>
+      </c>
+      <c r="C82">
+        <v>-4.671188314603459</v>
+      </c>
+      <c r="D82">
+        <v>7.26001168539654</v>
+      </c>
+      <c r="E82">
+        <v>18.3822</v>
+      </c>
+      <c r="F82">
+        <v>18.4712</v>
+      </c>
+      <c r="G82">
+        <v>6.54</v>
+      </c>
+      <c r="H82">
+        <v>23</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.15</v>
+      </c>
+      <c r="K82">
+        <v>0.579</v>
+      </c>
+      <c r="L82">
+        <v>1.571</v>
+      </c>
+      <c r="M82">
+        <v>4.41092256</v>
+      </c>
+      <c r="N82">
+        <v>-2.839922560000001</v>
+      </c>
+      <c r="O82">
+        <v>-0.7099806400000002</v>
+      </c>
+      <c r="P82">
+        <v>-2.12994192</v>
+      </c>
+      <c r="Q82">
+        <v>-1.55094192</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4710851185250947</v>
+      </c>
+      <c r="T82">
+        <v>3.566208590723769</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.08904032992136683</v>
+      </c>
+      <c r="W82">
+        <v>0.2175371692147776</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3561613196854673</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.270246759076841</v>
+      </c>
+      <c r="C83">
+        <v>-4.96138489119485</v>
+      </c>
+      <c r="D83">
+        <v>7.200705108805151</v>
+      </c>
+      <c r="E83">
+        <v>18.61309</v>
+      </c>
+      <c r="F83">
+        <v>18.70209</v>
+      </c>
+      <c r="G83">
+        <v>6.54</v>
+      </c>
+      <c r="H83">
+        <v>23</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.15</v>
+      </c>
+      <c r="K83">
+        <v>0.579</v>
+      </c>
+      <c r="L83">
+        <v>1.571</v>
+      </c>
+      <c r="M83">
+        <v>4.466059092000001</v>
+      </c>
+      <c r="N83">
+        <v>-2.895059092000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.7237647730000003</v>
+      </c>
+      <c r="P83">
+        <v>-2.171294319000001</v>
+      </c>
+      <c r="Q83">
+        <v>-1.592294319000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4938369668685207</v>
+      </c>
+      <c r="T83">
+        <v>3.75390377970923</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.08794106658900426</v>
+      </c>
+      <c r="W83">
+        <v>0.2177996732985458</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.351764266356017</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.272246759076841</v>
+      </c>
+      <c r="C84">
+        <v>-5.250620375536634</v>
+      </c>
+      <c r="D84">
+        <v>7.142359624463365</v>
+      </c>
+      <c r="E84">
+        <v>18.84398</v>
+      </c>
+      <c r="F84">
+        <v>18.93298</v>
+      </c>
+      <c r="G84">
+        <v>6.54</v>
+      </c>
+      <c r="H84">
+        <v>23</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.15</v>
+      </c>
+      <c r="K84">
+        <v>0.579</v>
+      </c>
+      <c r="L84">
+        <v>1.571</v>
+      </c>
+      <c r="M84">
+        <v>4.521195624000001</v>
+      </c>
+      <c r="N84">
+        <v>-2.950195624000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.7375489060000002</v>
+      </c>
+      <c r="P84">
+        <v>-2.212646718000001</v>
+      </c>
+      <c r="Q84">
+        <v>-1.633646718000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5191167983612164</v>
+      </c>
+      <c r="T84">
+        <v>3.962453989693077</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.08686861455743104</v>
+      </c>
+      <c r="W84">
+        <v>0.2180557748436855</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3474744582297241</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.274246759076841</v>
+      </c>
+      <c r="C85">
+        <v>-5.53891794230934</v>
+      </c>
+      <c r="D85">
+        <v>7.084952057690659</v>
+      </c>
+      <c r="E85">
+        <v>19.07487</v>
+      </c>
+      <c r="F85">
+        <v>19.16387</v>
+      </c>
+      <c r="G85">
+        <v>6.54</v>
+      </c>
+      <c r="H85">
+        <v>23</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.15</v>
+      </c>
+      <c r="K85">
+        <v>0.579</v>
+      </c>
+      <c r="L85">
+        <v>1.571</v>
+      </c>
+      <c r="M85">
+        <v>4.576332156</v>
+      </c>
+      <c r="N85">
+        <v>-3.005332156000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.7513330390000001</v>
+      </c>
+      <c r="P85">
+        <v>-2.253999117</v>
+      </c>
+      <c r="Q85">
+        <v>-1.674999117</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.547370727676582</v>
+      </c>
+      <c r="T85">
+        <v>4.195539518498553</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0858220047434861</v>
+      </c>
+      <c r="W85">
+        <v>0.2183057052672555</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3432880189739443</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.276246759076841</v>
+      </c>
+      <c r="C86">
+        <v>-5.826300027057354</v>
+      </c>
+      <c r="D86">
+        <v>7.028459972942644</v>
+      </c>
+      <c r="E86">
+        <v>19.30576</v>
+      </c>
+      <c r="F86">
+        <v>19.39476</v>
+      </c>
+      <c r="G86">
+        <v>6.54</v>
+      </c>
+      <c r="H86">
+        <v>23</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.15</v>
+      </c>
+      <c r="K86">
+        <v>0.579</v>
+      </c>
+      <c r="L86">
+        <v>1.571</v>
+      </c>
+      <c r="M86">
+        <v>4.631468688</v>
+      </c>
+      <c r="N86">
+        <v>-3.060468688</v>
+      </c>
+      <c r="O86">
+        <v>-0.7651171720000001</v>
+      </c>
+      <c r="P86">
+        <v>-2.295351516</v>
+      </c>
+      <c r="Q86">
+        <v>-1.716351516</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5791563981563681</v>
+      </c>
+      <c r="T86">
+        <v>4.457760738404709</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.08480031421082555</v>
+      </c>
+      <c r="W86">
+        <v>0.2185496849664549</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3392012568433022</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.278246759076841</v>
+      </c>
+      <c r="C87">
+        <v>-6.112788355423458</v>
+      </c>
+      <c r="D87">
+        <v>6.972861644576538</v>
+      </c>
+      <c r="E87">
+        <v>19.53665</v>
+      </c>
+      <c r="F87">
+        <v>19.62565</v>
+      </c>
+      <c r="G87">
+        <v>6.54</v>
+      </c>
+      <c r="H87">
+        <v>23</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.15</v>
+      </c>
+      <c r="K87">
+        <v>0.579</v>
+      </c>
+      <c r="L87">
+        <v>1.571</v>
+      </c>
+      <c r="M87">
+        <v>4.68660522</v>
+      </c>
+      <c r="N87">
+        <v>-3.11560522</v>
+      </c>
+      <c r="O87">
+        <v>-0.778901305</v>
+      </c>
+      <c r="P87">
+        <v>-2.336703915</v>
+      </c>
+      <c r="Q87">
+        <v>-1.757703915</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6151801580334595</v>
+      </c>
+      <c r="T87">
+        <v>4.754944787631691</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.08380266345540409</v>
+      </c>
+      <c r="W87">
+        <v>0.2187879239668495</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3352106538216163</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.280246759076841</v>
+      </c>
+      <c r="C88">
+        <v>-6.398403971006687</v>
+      </c>
+      <c r="D88">
+        <v>6.918136028993311</v>
+      </c>
+      <c r="E88">
+        <v>19.76754</v>
+      </c>
+      <c r="F88">
+        <v>19.85654</v>
+      </c>
+      <c r="G88">
+        <v>6.54</v>
+      </c>
+      <c r="H88">
+        <v>23</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.15</v>
+      </c>
+      <c r="K88">
+        <v>0.579</v>
+      </c>
+      <c r="L88">
+        <v>1.571</v>
+      </c>
+      <c r="M88">
+        <v>4.741741752</v>
+      </c>
+      <c r="N88">
+        <v>-3.170741752000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.7926854380000001</v>
+      </c>
+      <c r="P88">
+        <v>-2.378056314</v>
+      </c>
+      <c r="Q88">
+        <v>-1.799056314</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6563501693215636</v>
+      </c>
+      <c r="T88">
+        <v>5.094583701033955</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.08282821388034124</v>
+      </c>
+      <c r="W88">
+        <v>0.2190206225253745</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3313128555213649</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.282246759076841</v>
+      </c>
+      <c r="C89">
+        <v>-6.683167261918559</v>
+      </c>
+      <c r="D89">
+        <v>6.864262738081438</v>
+      </c>
+      <c r="E89">
+        <v>19.99843</v>
+      </c>
+      <c r="F89">
+        <v>20.08743</v>
+      </c>
+      <c r="G89">
+        <v>6.54</v>
+      </c>
+      <c r="H89">
+        <v>23</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.15</v>
+      </c>
+      <c r="K89">
+        <v>0.579</v>
+      </c>
+      <c r="L89">
+        <v>1.571</v>
+      </c>
+      <c r="M89">
+        <v>4.796878284</v>
+      </c>
+      <c r="N89">
+        <v>-3.225878284</v>
+      </c>
+      <c r="O89">
+        <v>-0.8064695710000001</v>
+      </c>
+      <c r="P89">
+        <v>-2.419408713</v>
+      </c>
+      <c r="Q89">
+        <v>-1.840408713</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7038540285001453</v>
+      </c>
+      <c r="T89">
+        <v>5.486474754959643</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.08187616544493502</v>
+      </c>
+      <c r="W89">
+        <v>0.2192479716917495</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.32750466177974</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.284246759076841</v>
+      </c>
+      <c r="C90">
+        <v>-6.967097986108133</v>
+      </c>
+      <c r="D90">
+        <v>6.811222013891866</v>
+      </c>
+      <c r="E90">
+        <v>20.22932</v>
+      </c>
+      <c r="F90">
+        <v>20.31832</v>
+      </c>
+      <c r="G90">
+        <v>6.54</v>
+      </c>
+      <c r="H90">
+        <v>23</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.15</v>
+      </c>
+      <c r="K90">
+        <v>0.579</v>
+      </c>
+      <c r="L90">
+        <v>1.571</v>
+      </c>
+      <c r="M90">
+        <v>4.852014816000001</v>
+      </c>
+      <c r="N90">
+        <v>-3.281014816000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.8202537040000002</v>
+      </c>
+      <c r="P90">
+        <v>-2.460761112000001</v>
+      </c>
+      <c r="Q90">
+        <v>-1.881761112000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7592751975418244</v>
+      </c>
+      <c r="T90">
+        <v>5.943680984539614</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.08094575447396984</v>
+      </c>
+      <c r="W90">
+        <v>0.219470153831616</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3237830178958793</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2862467590768411</v>
+      </c>
+      <c r="C91">
+        <v>-7.250215295521873</v>
+      </c>
+      <c r="D91">
+        <v>6.758994704478127</v>
+      </c>
+      <c r="E91">
+        <v>20.46021</v>
+      </c>
+      <c r="F91">
+        <v>20.54921</v>
+      </c>
+      <c r="G91">
+        <v>6.54</v>
+      </c>
+      <c r="H91">
+        <v>23</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.15</v>
+      </c>
+      <c r="K91">
+        <v>0.579</v>
+      </c>
+      <c r="L91">
+        <v>1.571</v>
+      </c>
+      <c r="M91">
+        <v>4.907151348</v>
+      </c>
+      <c r="N91">
+        <v>-3.336151348</v>
+      </c>
+      <c r="O91">
+        <v>-0.8340378370000001</v>
+      </c>
+      <c r="P91">
+        <v>-2.502113511</v>
+      </c>
+      <c r="Q91">
+        <v>-1.923113511</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8247729427728994</v>
+      </c>
+      <c r="T91">
+        <v>6.484015619497761</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.08003625161471176</v>
+      </c>
+      <c r="W91">
+        <v>0.2196873431144069</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.320145006458847</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2882467590768411</v>
+      </c>
+      <c r="C92">
+        <v>-7.532537759160519</v>
+      </c>
+      <c r="D92">
+        <v>6.707562240839481</v>
+      </c>
+      <c r="E92">
+        <v>20.6911</v>
+      </c>
+      <c r="F92">
+        <v>20.7801</v>
+      </c>
+      <c r="G92">
+        <v>6.54</v>
+      </c>
+      <c r="H92">
+        <v>23</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.15</v>
+      </c>
+      <c r="K92">
+        <v>0.579</v>
+      </c>
+      <c r="L92">
+        <v>1.571</v>
+      </c>
+      <c r="M92">
+        <v>4.962287880000001</v>
+      </c>
+      <c r="N92">
+        <v>-3.391287880000001</v>
+      </c>
+      <c r="O92">
+        <v>-0.8478219700000003</v>
+      </c>
+      <c r="P92">
+        <v>-2.543465910000001</v>
+      </c>
+      <c r="Q92">
+        <v>-1.964465910000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9033702370501893</v>
+      </c>
+      <c r="T92">
+        <v>7.132417181447538</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.07914695993010384</v>
+      </c>
+      <c r="W92">
+        <v>0.2198997059686912</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3165878397204153</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.290246759076841</v>
+      </c>
+      <c r="C93">
+        <v>-7.81408338509115</v>
+      </c>
+      <c r="D93">
+        <v>6.656906614908849</v>
+      </c>
+      <c r="E93">
+        <v>20.92199</v>
+      </c>
+      <c r="F93">
+        <v>21.01099</v>
+      </c>
+      <c r="G93">
+        <v>6.54</v>
+      </c>
+      <c r="H93">
+        <v>23</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.15</v>
+      </c>
+      <c r="K93">
+        <v>0.579</v>
+      </c>
+      <c r="L93">
+        <v>1.571</v>
+      </c>
+      <c r="M93">
+        <v>5.017424412</v>
+      </c>
+      <c r="N93">
+        <v>-3.446424412000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.8616061030000002</v>
+      </c>
+      <c r="P93">
+        <v>-2.584818309000001</v>
+      </c>
+      <c r="Q93">
+        <v>-2.005818309</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9994335967224326</v>
+      </c>
+      <c r="T93">
+        <v>7.924907979386154</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.07827721311768512</v>
+      </c>
+      <c r="W93">
+        <v>0.2201074015074968</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3131088524707404</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.292246759076841</v>
+      </c>
+      <c r="C94">
+        <v>-8.09486964146933</v>
+      </c>
+      <c r="D94">
+        <v>6.607010358530669</v>
+      </c>
+      <c r="E94">
+        <v>21.15288</v>
+      </c>
+      <c r="F94">
+        <v>21.24188</v>
+      </c>
+      <c r="G94">
+        <v>6.54</v>
+      </c>
+      <c r="H94">
+        <v>23</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.15</v>
+      </c>
+      <c r="K94">
+        <v>0.579</v>
+      </c>
+      <c r="L94">
+        <v>1.571</v>
+      </c>
+      <c r="M94">
+        <v>5.072560944</v>
+      </c>
+      <c r="N94">
+        <v>-3.501560944</v>
+      </c>
+      <c r="O94">
+        <v>-0.8753902360000001</v>
+      </c>
+      <c r="P94">
+        <v>-2.626170708</v>
+      </c>
+      <c r="Q94">
+        <v>-2.047170708</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.119512796312737</v>
+      </c>
+      <c r="T94">
+        <v>8.915521476809426</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.07742637384466682</v>
+      </c>
+      <c r="W94">
+        <v>0.2203105819258936</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3097054953786672</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.294246759076841</v>
+      </c>
+      <c r="C95">
+        <v>-8.374913476622874</v>
+      </c>
+      <c r="D95">
+        <v>6.557856523377127</v>
+      </c>
+      <c r="E95">
+        <v>21.38377</v>
+      </c>
+      <c r="F95">
+        <v>21.47277</v>
+      </c>
+      <c r="G95">
+        <v>6.54</v>
+      </c>
+      <c r="H95">
+        <v>23</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.15</v>
+      </c>
+      <c r="K95">
+        <v>0.579</v>
+      </c>
+      <c r="L95">
+        <v>1.571</v>
+      </c>
+      <c r="M95">
+        <v>5.127697476000001</v>
+      </c>
+      <c r="N95">
+        <v>-3.556697476000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.8891743690000002</v>
+      </c>
+      <c r="P95">
+        <v>-2.667523107000001</v>
+      </c>
+      <c r="Q95">
+        <v>-2.088523107000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.273900338643128</v>
+      </c>
+      <c r="T95">
+        <v>10.18916740206791</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.07659383219042307</v>
+      </c>
+      <c r="W95">
+        <v>0.220509392872927</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3063753287616923</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2962467590768409</v>
+      </c>
+      <c r="C96">
+        <v>-8.654231338245715</v>
+      </c>
+      <c r="D96">
+        <v>6.509428661754284</v>
+      </c>
+      <c r="E96">
+        <v>21.61466</v>
+      </c>
+      <c r="F96">
+        <v>21.70366</v>
+      </c>
+      <c r="G96">
+        <v>6.54</v>
+      </c>
+      <c r="H96">
+        <v>23</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.15</v>
+      </c>
+      <c r="K96">
+        <v>0.579</v>
+      </c>
+      <c r="L96">
+        <v>1.571</v>
+      </c>
+      <c r="M96">
+        <v>5.182834008</v>
+      </c>
+      <c r="N96">
+        <v>-3.611834008000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.9029585020000002</v>
+      </c>
+      <c r="P96">
+        <v>-2.708875506</v>
+      </c>
+      <c r="Q96">
+        <v>-2.129875506</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.47975039508365</v>
+      </c>
+      <c r="T96">
+        <v>11.88736196907924</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.07577900418839729</v>
+      </c>
+      <c r="W96">
+        <v>0.2207039737998107</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3031160167535891</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.298246759076841</v>
+      </c>
+      <c r="C97">
+        <v>-8.9328391917476</v>
+      </c>
+      <c r="D97">
+        <v>6.4617108082524</v>
+      </c>
+      <c r="E97">
+        <v>21.84555</v>
+      </c>
+      <c r="F97">
+        <v>21.93455</v>
+      </c>
+      <c r="G97">
+        <v>6.54</v>
+      </c>
+      <c r="H97">
+        <v>23</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.15</v>
+      </c>
+      <c r="K97">
+        <v>0.579</v>
+      </c>
+      <c r="L97">
+        <v>1.571</v>
+      </c>
+      <c r="M97">
+        <v>5.237970540000001</v>
+      </c>
+      <c r="N97">
+        <v>-3.666970540000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.9167426350000003</v>
+      </c>
+      <c r="P97">
+        <v>-2.750227905000001</v>
+      </c>
+      <c r="Q97">
+        <v>-2.171227905000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.767940474100381</v>
+      </c>
+      <c r="T97">
+        <v>14.26483436289509</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.07498133046009837</v>
+      </c>
+      <c r="W97">
+        <v>0.2208944582861285</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2999253218403934</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.300246759076841</v>
+      </c>
+      <c r="C98">
+        <v>-9.21075253780252</v>
+      </c>
+      <c r="D98">
+        <v>6.414687462197477</v>
+      </c>
+      <c r="E98">
+        <v>22.07644</v>
+      </c>
+      <c r="F98">
+        <v>22.16544</v>
+      </c>
+      <c r="G98">
+        <v>6.54</v>
+      </c>
+      <c r="H98">
+        <v>23</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.15</v>
+      </c>
+      <c r="K98">
+        <v>0.579</v>
+      </c>
+      <c r="L98">
+        <v>1.571</v>
+      </c>
+      <c r="M98">
+        <v>5.293107072</v>
+      </c>
+      <c r="N98">
+        <v>-3.722107072</v>
+      </c>
+      <c r="O98">
+        <v>-0.930526768</v>
+      </c>
+      <c r="P98">
+        <v>-2.791580304</v>
+      </c>
+      <c r="Q98">
+        <v>-2.212580304</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.200225592625471</v>
+      </c>
+      <c r="T98">
+        <v>17.83104295361882</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.07420027493447236</v>
+      </c>
+      <c r="W98">
+        <v>0.221080974345648</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2968010997378894</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.302246759076841</v>
+      </c>
+      <c r="C99">
+        <v>-9.487986429136516</v>
+      </c>
+      <c r="D99">
+        <v>6.368343570863482</v>
+      </c>
+      <c r="E99">
+        <v>22.30733</v>
+      </c>
+      <c r="F99">
+        <v>22.39633</v>
+      </c>
+      <c r="G99">
+        <v>6.54</v>
+      </c>
+      <c r="H99">
+        <v>23</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.15</v>
+      </c>
+      <c r="K99">
+        <v>0.579</v>
+      </c>
+      <c r="L99">
+        <v>1.571</v>
+      </c>
+      <c r="M99">
+        <v>5.348243604</v>
+      </c>
+      <c r="N99">
+        <v>-3.777243604000001</v>
+      </c>
+      <c r="O99">
+        <v>-0.9443109010000001</v>
+      </c>
+      <c r="P99">
+        <v>-2.832932703</v>
+      </c>
+      <c r="Q99">
+        <v>-2.253932703</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.920700790167295</v>
+      </c>
+      <c r="T99">
+        <v>23.77472393815844</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.07343532364648811</v>
+      </c>
+      <c r="W99">
+        <v>0.2212636447132187</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2937412945859523</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.304246759076841</v>
+      </c>
+      <c r="C100">
+        <v>-9.764555486592929</v>
+      </c>
+      <c r="D100">
+        <v>6.322664513407068</v>
+      </c>
+      <c r="E100">
+        <v>22.53822</v>
+      </c>
+      <c r="F100">
+        <v>22.62722</v>
+      </c>
+      <c r="G100">
+        <v>6.54</v>
+      </c>
+      <c r="H100">
+        <v>23</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.15</v>
+      </c>
+      <c r="K100">
+        <v>0.579</v>
+      </c>
+      <c r="L100">
+        <v>1.571</v>
+      </c>
+      <c r="M100">
+        <v>5.403380136</v>
+      </c>
+      <c r="N100">
+        <v>-3.832380136</v>
+      </c>
+      <c r="O100">
+        <v>-0.9580950340000001</v>
+      </c>
+      <c r="P100">
+        <v>-2.874285102</v>
+      </c>
+      <c r="Q100">
+        <v>-2.295285102</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.361651185250942</v>
+      </c>
+      <c r="T100">
+        <v>35.66208590723765</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.07268598360927905</v>
+      </c>
+      <c r="W100">
+        <v>0.2214425871141042</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2907439344371161</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.306246759076841</v>
+      </c>
+      <c r="C101">
+        <v>-10.04047391451122</v>
+      </c>
+      <c r="D101">
+        <v>6.277636085488784</v>
+      </c>
+      <c r="E101">
+        <v>22.76911</v>
+      </c>
+      <c r="F101">
+        <v>22.85811</v>
+      </c>
+      <c r="G101">
+        <v>6.54</v>
+      </c>
+      <c r="H101">
+        <v>23</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.15</v>
+      </c>
+      <c r="K101">
+        <v>0.579</v>
+      </c>
+      <c r="L101">
+        <v>1.571</v>
+      </c>
+      <c r="M101">
+        <v>5.458516668000001</v>
+      </c>
+      <c r="N101">
+        <v>-3.887516668000001</v>
+      </c>
+      <c r="O101">
+        <v>-0.9718791670000002</v>
+      </c>
+      <c r="P101">
+        <v>-2.915637501000001</v>
+      </c>
+      <c r="Q101">
+        <v>-2.336637501000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.684502370501884</v>
+      </c>
+      <c r="T101">
+        <v>71.32417181447529</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.07195178175463986</v>
+      </c>
+      <c r="W101">
+        <v>0.221617914516992</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2878071270185594</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
